--- a/data_extactor/batch/801_850.xlsx
+++ b/data_extactor/batch/801_850.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43AAB7B-49A2-463E-AF53-97D7163EE877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1633 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="540">
+  <si>
+    <t>49-3093.00</t>
+  </si>
+  <si>
+    <t>Tire Repairers and Changers</t>
+  </si>
+  <si>
+    <t>Alignment Technician | Lube Technician | Service Technician | Tire Buster | Tire Changer | Tire Installer | Tire Repairer | Tire Shop Mechanic | Tire Technician</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Outlook | Microsoft Word | Project estimation software | Recordkeeping software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Administration and Management | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Manual Dexterity | Multilimb Coordination | Static Strength | Near Vision | Extent Flexibility | Problem Sensitivity | Speech Clarity | Control Precision | Finger Dexterity | Arm-Hand Steadiness | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Indoors, Not Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Work With or Contribute to a Work Group or Team | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Deal With External Customers or the Public in General | Time Pressure | Frequency of Decision Making | Spend Time Bending or Twisting Your Body | Spend Time Walking or Running | Telephone Conversations | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Impact of Decisions on Co-workers or Company Results | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Exposed to Hazardous Equipment | In an Enclosed Vehicle or Operate Enclosed Equipment | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Consequence of Error | Work Outcomes and Results of Other Workers | Physical Proximity | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Automotive Body and Related Repairers | Automotive Glass Installers and Repairers | Automotive Service Technicians and Mechanics | Automotive and Watercraft Service Attendants | Bicycle Repairers | Bus and Truck Mechanics and Diesel Engine Specialists | Cleaners of Vehicles and Equipment | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Grinding and Polishing Workers, Hand | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Mobile Heavy Equipment Mechanics, Except Engines | Motorcycle Mechanics | Outdoor Power Equipment and Other Small Engine Mechanics | Rail Car Repairers | Rail-Track Laying and Maintenance Equipment Operators | Tire Builders</t>
+  </si>
+  <si>
+    <t>Repair and replace tires.</t>
+  </si>
+  <si>
+    <t>Apply rubber cement to buffed tire casings prior to vulcanization process. | Assist mechanics and perform various mechanical duties, such as changing oil or checking and replacing batteries. | Buff defective areas of inner tubes, using scrapers. | Clean and tidy up the shop. | Clean sides of whitewall tires. | Drive automobile or service trucks to industrial sites to provide services or respond to emergency calls. | Glue tire patches over ruptures in tire casings, using rubber cement. | Hammer required counterweights onto rims of wheels. | Identify tire size and ply and inflate tires accordingly. | Inflate inner tubes and immerse them in water to locate leaks. | Inspect tire casings for defects, such as holes or tears. | Locate punctures in tubeless tires by visual inspection or by immersing inflated tires in water baths and observing air bubbles. | Order replacements for tires or tubes. | Patch tubes with adhesive rubber patches or seal rubber patches to tubes, using hot vulcanizing plates. | Place wheels on balancing machines to determine counterweights required to balance wheels. | Prepare rims and wheel drums for reassembly by scraping, grinding, or sandblasting. | Raise vehicles, using hydraulic jacks. | Reassemble tires onto wheels. | Remount wheels onto vehicles. | Replace valve stems and remove puncturing objects. | Rotate tires to different positions on vehicles, using hand tools. | Seal punctures in tubeless tires by inserting adhesive material and expanding rubber plugs into punctures, using hand tools. | Separate tubed tires from wheels, using rubber mallets and metal bars or mechanical tire changers. | Unbolt and remove wheels from vehicles, using lug wrenches or other hand or power tools.</t>
+  </si>
+  <si>
+    <t>49-9011.00</t>
+  </si>
+  <si>
+    <t>Mechanical Door Repairers</t>
+  </si>
+  <si>
+    <t>Commercial Door Installer | Commercial Installer | Door Installer | Door Technician | Garage Door Installer | Garage Door Technician | Installation Technician | Residential Door Installer | Service Technician</t>
+  </si>
+  <si>
+    <t>Facebook | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Route mapping software | Web browser software | Work order software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Monitoring | Active Learning</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Building and Construction | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Arm-Hand Steadiness | Near Vision | Problem Sensitivity | Trunk Strength | Extent Flexibility | Static Strength | Finger Dexterity | Oral Comprehension | Speech Clarity | Speech Recognition | Multilimb Coordination | Control Precision | Information Ordering | Oral Expression | Written Comprehension | Visualization | Inductive Reasoning | Deductive Reasoning | Written Expression | Depth Perception | Visual Color Discrimination | Gross Body Equilibrium | Gross Body Coordination</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | In an Enclosed Vehicle or Operate Enclosed Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Outdoors, Exposed to All Weather Conditions | Exposed to High Places | Exposed to Hazardous Equipment | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Time Pressure | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Physical Proximity | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Indoors, Not Environmentally Controlled | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Outdoors, Under Cover | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Glass Installers and Repairers | Carpenters | Control and Valve Installers and Repairers, Except Mechanical Door | Electricians | Electronic Equipment Installers and Repairers, Motor Vehicles | Elevator and Escalator Installers and Repairers | Fence Erectors | Glaziers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Insulation Workers, Floor, Ceiling, and Wall | Locksmiths and Safe Repairers | Maintenance and Repair Workers, General | Mobile Heavy Equipment Mechanics, Except Engines | Plumbers, Pipefitters, and Steamfitters | Rail Car Repairers | Sheet Metal Workers | Structural Iron and Steel Workers</t>
+  </si>
+  <si>
+    <t>Install, service, or repair automatic door mechanisms and hydraulic doors. Includes garage door mechanics.</t>
+  </si>
+  <si>
+    <t>Adjust doors to open or close with the correct amount of effort, or make simple adjustments to electric openers. | Assemble and fasten tracks to structures or bucks, using impact wrenches or welding equipment. | Bore or cut holes in flooring as required for installation, using hand or power tools. | Carry springs to tops of doors, using ladders or scaffolding, and attach springs to tracks to install spring systems. | Clean door closer parts, using caustic soda, rotary brushes, or grinding wheels. | Collect payment upon job completion. | Complete required paperwork, such as work orders, according to services performed or required. | Cover treadles with carpeting or other floor covering materials, and test systems by operating treadles. | Cut door stops or angle irons to fit openings. | Fabricate replacements for worn or broken parts, using welders, lathes, drill presses, or shaping or milling machines. | Fasten angle iron back-hangers to ceilings and tracks, using fasteners or welding equipment. | Inspect job sites, assessing headroom, side room, or other conditions to determine appropriateness of door for a given location. | Install dock seals, bumpers, or shelters. | Install door frames, rails, steel rolling curtains, electronic-eye mechanisms, or electric door openers and closers, using power tools, hand tools, and electronic test equipment. | Lubricate door closer oil chambers, and pack spindles with leather washers. | Operate lifts, winches, or chain falls to move heavy curtain doors. | Order replacement springs, sections, or slats. | Prepare doors for hardware installation, such as drilling holes to install locks. | Remove or disassemble defective automatic mechanical door closers, using hand tools. | Repair or replace worn or broken door parts, using hand tools. | Run low voltage wiring on ceiling surfaces, using insulated staples. | Set doors into place or stack hardware sections into openings after rail or track installation. | Set in and secure floor treadles for door-activating mechanisms, and connect power packs and electrical panelboards to treadles. | Study blueprints and schematic diagrams to determine appropriate methods of installing or repairing automated door openers. | Wind large springs with upward motion of arm.</t>
+  </si>
+  <si>
+    <t>49-9012.00</t>
+  </si>
+  <si>
+    <t>Control and Valve Installers and Repairers, Except Mechanical Door</t>
+  </si>
+  <si>
+    <t>Control Valve Mechanic | Control Valve Technician | Electric Meter Technician | Instrument Technician | Instrument and Electrical Technician (I and E Technician) | Measurement Technician | Meter Technician | Service Technician | Valve Technician | Water Plant Maintenance Mechanic</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Emerson FIRSTVUE Value Sizing | Graphical user interface GUI design software | IBM Maximo Asset Management | Ladder Logic | Maintenance record software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Oracle Primavera Enterprise Project Portfolio Management | Programmable logic controller PLC software | SAP software | Structured query language SQL | Supervisory control and data acquisition SCADA software | Wonderware software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Listening | Writing | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Engineering and Technology | Public Safety and Security | Customer and Personal Service | Computers and Electronics | Mathematics | Design | Production and Processing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Near Vision | Oral Expression | Arm-Hand Steadiness | Information Ordering | Deductive Reasoning | Manual Dexterity | Speech Recognition | Extent Flexibility | Multilimb Coordination | Finger Dexterity | Category Flexibility | Inductive Reasoning | Written Expression | Written Comprehension | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Control Precision | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Outdoors, Exposed to All Weather Conditions | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Health and Safety of Other Workers | In an Enclosed Vehicle or Operate Enclosed Equipment | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Time Pressure | Indoors, Not Environmentally Controlled | E-Mail | Exposed to Very Hot or Cold Temperatures | Exposed to Hazardous Conditions | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Frequency of Decision Making | Exposed to Hazardous Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Consequence of Error | Determine Tasks, Priorities and Goals | Exposed to Minor Burns, Cuts, Bites, or Stings | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions | Exposed to Cramped Work Space, Awkward Positions | Physical Proximity | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Boilermakers | Calibration Technologists and Technicians | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Gas Compressor and Gas Pumping Station Operators | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Mechanical Engineers | Mobile Heavy Equipment Mechanics, Except Engines | Plumbers, Pipefitters, and Steamfitters | Rail Car Repairers | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Install, repair, and maintain mechanical regulating and controlling devices, such as electric meters, gas regulators, thermostats, safety and flow valves, and other mechanical governors.</t>
+  </si>
+  <si>
+    <t>Advise customers on proper installation of valves or regulators and related equipment. | Attach air hoses to meter inlets, plug outlets, and observe gauges for pressure losses to test internal seams for leaks. | Calibrate instrumentation, such as meters, gauges, and regulators, for pressure, temperature, flow, and level. | Clean internal compartments and moving parts, using rags and cleaning compounds. | Clean plant growth, scale, paint, soil, or rust from meter housings, using wire brushes, scrapers, buffers, sandblasters, or cleaning compounds. | Connect hoses from provers to meter inlets and outlets, and raise prover bells until prover gauges register zero. | Connect regulators to test stands, and turn screw adjustments until gauges indicate that inlet and outlet pressures meet specifications. | Cut seats to receive new orifices, tap inspection ports, and perform other repairs to salvage usable materials, using hand tools and machine tools. | Disassemble and repair mechanical control devices or valves, such as regulators, thermostats, or hydrants, using power tools, hand tools, and cutting torches. | Disconnect or remove defective or unauthorized meters, using hand tools. | Dismantle meters, and replace or adjust defective parts such as cases, shafts, gears, disks, and recording mechanisms, using soldering irons and hand tools. | Examine valves or mechanical control device parts for defects, dents, or loose attachments, and mark malfunctioning areas of defective units. | Install regulators and related equipment such as gas meters, odorization units, and gas pressure telemetering equipment. | Install, inspect and test electric meters, relays, and power sources to detect causes of malfunctions and inaccuracies, using hand tools and testing equipment. | Investigate instances of illegal tapping into service lines. | Lubricate wearing surfaces of mechanical parts, using oils or other lubricants. | Make adjustments to meter components, such as setscrews or timing mechanisms, so that they conform to specifications. | Measure tolerances of assembled and salvageable parts for conformance to standards or specifications, using gauges, micrometers, and calipers. | Mount and install meters and other electric equipment such as time clocks, transformers, and circuit breakers, using electricians' hand tools. | Record maintenance information, including test results, material usage, and repairs made. | Record meter readings and installation data on meter cards, work orders, or field service orders, or enter data into hand-held computers. | Repair electric meters and components, such as transformers and relays, and replace metering devices, dial glasses, and faulty or incorrect wiring, using hand tools. | Repair leaks in valve seats or bellows of automotive heater thermostats, using soft solder, flux, and acetylene torches. | Replace defective parts, such as bellows, range springs, and toggle switches, and reassemble units according to blueprints, using cam presses and hand tools. | Report hazardous field situations and damaged or missing meters. | Shut off service and notify repair crews when major repairs are required, such as the replacement of underground pipes or wiring. | Splice and connect cables from meters or current transformers to pull boxes or switchboards, using hand tools. | Test valves and regulators for leaks and accurate temperature and pressure settings, using precision testing equipment. | Trace and tag meters or house lines. | Turn meters on or off to establish or close service. | Turn valves to allow measured amounts of air or gas to pass through meters at specified flow rates. | Vary air pressure flowing into regulators and turn handles to assess functioning of valves and pistons.</t>
+  </si>
+  <si>
+    <t>49-9021.00</t>
+  </si>
+  <si>
+    <t>Heating, Air Conditioning, and Refrigeration Mechanics and Installers</t>
+  </si>
+  <si>
+    <t>A/C Tech (Air Conditioning Technician) | HVAC Installer (Heating, Ventilation, and Air Conditioning Installer) | HVAC Mechanic (Heating, Ventilation, and Air Conditioning Mechanic) | HVAC Service Tech (Heating, Ventilation, and Air Conditioning Service Technician) | HVAC Specialist (Heating, Ventilation, and Air Conditioning Specialist) | HVAC Tech (Heating, Ventilation, and Air Conditioning Technician) | Refrigeration Mechanic | Refrigeration Operator | Refrigeration Technician (Refrigeration Tech) | Service Technician (Service Tech)</t>
+  </si>
+  <si>
+    <t>Adobe Acrobat | Alerton Ascent Compass | Atlas Construction Business Forms | Autodesk AutoCAD | Building automation software | Computerized maintenance management system CMMS | Contact management systems | Cworks CMMS | Data logging software | Database software | Delta Controls inteliWEB | Facility energy management software | Graphics software | HVAC tools software | Honeywell WEBs-N4 | IBM Maximo Asset Management | IBM Notes | Johnson Controls Metasys | ManagerPlus | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | Siemens APOGEE Building Automation Software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Speaking | Active Learning | Monitoring</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Customer and Personal Service | Engineering and Technology | Computers and Electronics | English Language | Public Safety and Security | Design | Physics | Mathematics | Administration and Management | Education and Training</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Deductive Reasoning | Oral Comprehension | Arm-Hand Steadiness | Finger Dexterity | Visual Color Discrimination | Inductive Reasoning | Manual Dexterity | Visualization | Oral Expression | Information Ordering | Category Flexibility | Multilimb Coordination | Extent Flexibility | Speech Clarity | Static Strength | Control Precision | Flexibility of Closure | Written Comprehension | Speech Recognition | Hearing Sensitivity | Far Vision | Trunk Strength | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Exposed to Contaminants | Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Indoors, Not Environmentally Controlled | Work Outcomes and Results of Other Workers | Spend Time Standing | Exposed to High Places | Deal With External Customers or the Public in General | E-Mail | Exposed to Cramped Work Space, Awkward Positions | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Time Pressure | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error | Exposed to Hazardous Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Service Technicians and Mechanics | Biomass Plant Technicians | Boilermakers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Engine and Other Machine Assemblers | Geothermal Technicians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Home Appliance Repairers | Industrial Machinery Mechanics | Insulation Workers, Floor, Ceiling, and Wall | Maintenance and Repair Workers, General | Mechanical Engineers | Plumbers, Pipefitters, and Steamfitters | Sheet Metal Workers | Solar Thermal Installers and Technicians | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Install or repair heating, central air conditioning, HVAC, or refrigeration systems, including oil burners, hot-air furnaces, and heating stoves.</t>
+  </si>
+  <si>
+    <t>Adjust system controls to settings recommended by manufacturer to balance system. | Braze or solder parts to repair defective joints and leaks. | Comply with all applicable standards, policies, or procedures, such as safety procedures or the maintenance of a clean work area. | Connect heating or air conditioning equipment to fuel, water, or refrigerant source to form complete circuit. | Cut or drill holes in floors, walls, or roof to install equipment, using power saws or drills. | Discuss heating or cooling system malfunctions with users to isolate problems or to verify that repairs corrected malfunctions. | Estimate, order, pick up, deliver, and install materials and supplies needed to maintain equipment in good working condition. | Inspect and test systems to verify system compliance with plans and specifications or to detect and locate malfunctions. | Install auxiliary components to heating or cooling equipment, such as expansion or discharge valves, air ducts, pipes, blowers, dampers, flues, or stokers. | Install dehumidifiers or related equipment for spaces that require cool, dry air to operate efficiently, such as computer rooms. | Install expansion and control valves, using acetylene torches and wrenches. | Install or repair air purification systems, such as specialized filters or ultraviolet (UV) light purification systems. | Install or repair self-contained ground source heat pumps or hybrid ground or air source heat pumps to minimize carbon-based energy consumption and reduce carbon emissions. | Install, connect, or adjust thermostats, humidistats, or timers. | Keep records of repairs and replacements made and causes of malfunctions. | Lay out and connect electrical wiring between controls and equipment, according to wiring diagrams, using electrician's hand tools. | Lay out reference points for installation of structural and functional components, using measuring instruments. | Lift and align components into position, using hoist or block and tackle. | Measure, cut, thread, or bend pipe or tubing, using pipe fitter's tools. | Mount compressor, condenser, and other components in specified locations on frames, using hand tools and acetylene welding equipment. | Perform mechanical overhauls and refrigerant reclaiming. | Recommend, develop, or perform preventive or general maintenance procedures, such as cleaning, power-washing, or vacuuming equipment, oiling parts, or changing filters. | Record and report time, materials, faults, deficiencies, or other unusual occurrences on work orders. | Repair or replace defective equipment, components, or wiring. | Repair or service heating, ventilating, and air conditioning (HVAC) systems to improve efficiency, such as by changing filters, cleaning ducts, and refilling non-toxic refrigerants. | Schedule work with customers and initiate work orders, house requisitions, and orders from stock. | Study blueprints, design specifications, or manufacturers' recommendations to ascertain the configuration of heating or cooling equipment components and to ensure the proper installation of components. | Supervise and instruct assistants. | Test electrical circuits or components for continuity, using electrical test equipment. | Test pipes, lines, components, and connections for leaks.</t>
+  </si>
+  <si>
+    <t>49-9031.00</t>
+  </si>
+  <si>
+    <t>Home Appliance Repairers</t>
+  </si>
+  <si>
+    <t>Appliance Mechanic | Appliance Repair Mechanic | Appliance Repair Technician (Appliance Repair Tech) | Appliance Service Technician | Appliance Technician (Appliance Tech) | Repair Man | Repair Technician | Service Technician (Service Tech) | Vacuum Repairer</t>
+  </si>
+  <si>
+    <t>Intac International Wintac | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word | Parts database software | RazorSync | Route mapping software | ServiceMax | Web browser software | dESCO ESC</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mechanical | English Language | Administration and Management | Administrative | Computers and Electronics | Sales and Marketing | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Problem Sensitivity | Manual Dexterity | Finger Dexterity | Near Vision | Oral Expression | Oral Comprehension | Information Ordering | Visualization | Extent Flexibility | Deductive Reasoning | Written Comprehension | Inductive Reasoning | Fluency of Ideas | Written Expression | Visual Color Discrimination | Trunk Strength | Static Strength | Multilimb Coordination | Control Precision | Selective Attention | Flexibility of Closure | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Frequency of Decision Making | Importance of Being Exact or Accurate | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Exposed to Cramped Work Space, Awkward Positions | Indoors, Environmentally Controlled | Impact of Decisions on Co-workers or Company Results | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Time Pressure | Indoors, Not Environmentally Controlled | Physical Proximity | Work With or Contribute to a Work Group or Team | E-Mail | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Automotive Service Technicians and Mechanics | Boilermakers | Cleaners of Vehicles and Equipment | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Engine and Other Machine Assemblers | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Installation, Maintenance, and Repair Workers | Industrial Machinery Mechanics | Lighting Technicians | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Mechanical Engineers | Outdoor Power Equipment and Other Small Engine Mechanics | Plumbers, Pipefitters, and Steamfitters</t>
+  </si>
+  <si>
+    <t>Repair, adjust, or install all types of electric or gas household appliances, such as refrigerators, washers, dryers, and ovens.</t>
+  </si>
+  <si>
+    <t>Assemble new or reconditioned appliances. | Bill customers for repair work, and collect payment. | Clean and reinstall parts. | Clean, lubricate, and touch up minor defects on newly installed or repaired appliances. | Conserve, recover, and recycle refrigerants used in cooling systems. | Contact supervisors or offices to receive repair assignments. | Disassemble appliances so that problems can be diagnosed and repairs can be made. | Install appliances such as refrigerators, washing machines, and stoves. | Install gas pipes and water lines to connect appliances to existing gas lines or plumbing. | Instruct customers regarding operation and care of appliances, and provide information such as emergency service numbers. | Level refrigerators, adjust doors, and connect water lines to water pipes for ice makers and water dispensers, using hand tools. | Level washing machines and connect hoses to water pipes, using hand tools. | Light and adjust pilot lights on gas stoves, and examine valves and burners for gas leakage and specified flame. | Maintain stocks of parts used in on-site installation, maintenance, and repair of appliances. | Measure, cut, and thread pipe, and connect it to feeder lines and equipment or appliances, using rules and hand tools. | Observe and examine appliances during operation to detect specific malfunctions such as loose parts or leaking fluid. | Observe and test operation of appliances following installation, and make any initial installation adjustments that are necessary. | Provide repair cost estimates, and recommend whether appliance repair or replacement is a better choice. | Reassemble units after repairs are made, making adjustments and cleaning and lubricating parts as needed. | Record maintenance and repair work performed on appliances. | Refer to schematic drawings, product manuals, and troubleshooting guides to diagnose and repair problems. | Replace worn and defective parts such as switches, bearings, transmissions, belts, gears, circuit boards, or defective wiring. | Respond to emergency calls for problems such as gas leaks. | Service and repair domestic electrical or gas appliances, such as clothes washers, refrigerators, stoves, and dryers. | Set appliance thermostats, and check to ensure that they are functioning properly. | Take measurements to determine if appliances will fit in installation locations, performing minor carpentry work when necessary to ensure proper installation. | Talk to customers or refer to work orders to establish the nature of appliance malfunctions. | Test and examine gas pipelines and equipment to locate leaks and faulty connections, and to determine the pressure and flow of gas. | Trace electrical circuits, following diagrams, and conduct tests with circuit testers and other equipment to locate shorts and grounds.</t>
+  </si>
+  <si>
+    <t>49-9041.00</t>
+  </si>
+  <si>
+    <t>Industrial Machinery Mechanics</t>
+  </si>
+  <si>
+    <t>Industrial Machinery Mechanic | Industrial Mechanic | Loom Fixer | Loom Technician | Machine Adjuster | Machine Mechanic | Maintenance Technician | Mechanic | Overhauler | Sewing Machine Mechanic</t>
+  </si>
+  <si>
+    <t>BIT Corp ProMACS PLC | Extranet Machine Tools Suite | Inventory tracking software | KEYENCE PLC Ladder Logic | Maintenance management software | Maintenance planning and control software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Programmable logic controller PLC software | SAP software | Supervisory control and data acquisition SCADA software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Active Learning | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Production and Processing | Engineering and Technology | Design | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Manual Dexterity | Finger Dexterity | Control Precision | Near Vision | Reaction Time | Arm-Hand Steadiness | Multilimb Coordination | Hearing Sensitivity | Information Ordering | Selective Attention | Visualization | Auditory Attention | Extent Flexibility | Trunk Strength | Static Strength | Deductive Reasoning | Written Comprehension | Response Orientation | Perceptual Speed | Category Flexibility | Inductive Reasoning | Oral Expression | Oral Comprehension | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Not Environmentally Controlled | Freedom to Make Decisions | Importance of Being Exact or Accurate | Time Pressure | Physical Proximity | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Control and Valve Installers and Repairers, Except Mechanical Door | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Repair, install, adjust, or maintain industrial production and processing machinery or refinery and pipeline distribution systems. May also install, dismantle, or move machinery and heavy equipment according to plans.</t>
+  </si>
+  <si>
+    <t>Analyze test results, machine error messages, or information obtained from operators to diagnose equipment problems. | Assign schedules to work crews. | Clean, lubricate, or adjust parts, equipment, or machinery. | Cut and weld metal to repair broken metal parts, fabricate new parts, or assemble new equipment. | Demonstrate equipment functions and features to machine operators. | Disassemble machinery or equipment to remove parts and make repairs. | Enter codes and instructions to program computer-controlled machinery. | Examine parts for defects, such as breakage or excessive wear. | Observe and test the operation of machinery or equipment to diagnose malfunctions, using voltmeters or other testing devices. | Operate newly repaired machinery or equipment to verify the adequacy of repairs. | Reassemble equipment after completion of inspections, testing, or repairs. | Record parts or materials used and order or requisition new parts or materials, as necessary. | Record repairs and maintenance performed. | Repair or maintain the operating condition of industrial production or processing machinery or equipment. | Repair or replace broken or malfunctioning components of machinery or equipment. | Study blueprints or manufacturers' manuals to determine correct installation or operation of machinery.</t>
+  </si>
+  <si>
+    <t>49-9043.00</t>
+  </si>
+  <si>
+    <t>Maintenance Workers, Machinery</t>
+  </si>
+  <si>
+    <t>Lubricator | Machine Repairer | Maintainer | Maintenance Craftsman | Maintenance Man | Maintenance Mechanic | Maintenance Technician (Maintenance Tech) | Maintenance Worker | Oiler | Overhauler</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system software CMMS | Database software | Management information systems MIS | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | Scheduling software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Administration and Management | English Language | Design</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Problem Sensitivity | Near Vision | Manual Dexterity | Control Precision | Extent Flexibility | Multilimb Coordination | Visualization | Selective Attention | Perceptual Speed | Flexibility of Closure | Information Ordering | Inductive Reasoning | Deductive Reasoning | Oral Expression | Visual Color Discrimination | Trunk Strength | Static Strength | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Freedom to Make Decisions | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Consequence of Error | Exposed to Hazardous Equipment | Frequency of Decision Making | E-Mail | Exposed to Hazardous Conditions | Indoors, Not Environmentally Controlled | Time Pressure | Spend Time Walking or Running | Importance of Repeating Same Tasks | Work Outcomes and Results of Other Workers | Indoors, Environmentally Controlled | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Control and Valve Installers and Repairers, Except Mechanical Door | Cutting and Slicing Machine Setters, Operators, and Tenders | Electric Motor, Power Tool, and Related Repairers | Engine and Other Machine Assemblers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Helpers--Installation, Maintenance, and Repair Workers | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Mobile Heavy Equipment Mechanics, Except Engines | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rail Car Repairers | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Lubricate machinery, change parts, or perform other routine machinery maintenance.</t>
+  </si>
+  <si>
+    <t>Clean machines and machine parts, using cleaning solvents, cloths, air guns, hoses, vacuums, or other equipment. | Collaborate with other workers to repair or move machines, machine parts, or equipment. | Collect and discard worn machine parts and other refuse to maintain machinery and work areas. | Dismantle machines and remove parts for repair, using hand tools, chain falls, jacks, cranes, or hoists. | Inspect or test damaged machine parts, and mark defective areas or advise supervisors of repair needs. | Install, replace, or change machine parts and attachments, according to production specifications. | Inventory and requisition machine parts, equipment, and other supplies so that stock can be maintained and replenished. | Lubricate or apply adhesives or other materials to machines, machine parts, or other equipment according to specified procedures. | Measure, mix, prepare, and test chemical solutions used to clean or repair machinery and equipment. | Read work orders and specifications to determine machines and equipment requiring repair or maintenance. | Reassemble machines after the completion of repair or maintenance work. | Record production, repair, and machine maintenance information. | Remove hardened material from machines or machine parts, using abrasives, power and hand tools, jackhammers, sledgehammers, or other equipment. | Replace or repair metal, wood, leather, glass, or other lining in machines, or in equipment compartments or containers. | Replace, empty, or replenish machine and equipment containers such as gas tanks or boxes. | Set up and operate machines, and adjust controls to regulate operations. | Start machines and observe mechanical operation to determine efficiency and to detect problems. | Transport machine parts, tools, equipment, and other material between work areas and storage, using cranes, hoists, or dollies.</t>
+  </si>
+  <si>
+    <t>49-9044.00</t>
+  </si>
+  <si>
+    <t>Millwrights</t>
+  </si>
+  <si>
+    <t>Maintenance Mechanic | Maintenance Millwright | Millwright | Millwright Business Representative (Millwright Business Rep) | Millwright Foreman | Millwright General Foreman | Millwright Instructor | Precision Millwright</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Monitoring | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics | Building and Construction | Education and Training | Engineering and Technology | Public Safety and Security | English Language | Design | Production and Processing | Physics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Control Precision | Multilimb Coordination | Static Strength | Trunk Strength | Extent Flexibility | Information Ordering | Problem Sensitivity | Oral Comprehension | Hearing Sensitivity | Far Vision | Reaction Time | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Oral Expression | Response Orientation | Selective Attention | Category Flexibility | Speech Clarity | Speech Recognition | Auditory Attention | Gross Body Equilibrium | Dynamic Strength | Rate Control</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Not Environmentally Controlled | Exposed to Hazardous Equipment | Contact With Others | Consequence of Error | Physical Proximity | Outdoors, Exposed to All Weather Conditions | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Exposed to Contaminants | Spend Time Standing | Telephone Conversations | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Very Hot or Cold Temperatures | Exposed to Cramped Work Space, Awkward Positions | Exposed to Extremely Bright or Inadequate Lighting Conditions | E-Mail | Work Outcomes and Results of Other Workers | Importance of Repeating Same Tasks | Spend Time Bending or Twisting Your Body | Exposed to High Places | Exposed to Hazardous Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Outdoors, Under Cover | Exposed to Minor Burns, Cuts, Bites, or Stings | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Industrial Machinery Mechanics | Machinists | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Riggers | Robotics Technicians | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Install, dismantle, or move machinery and heavy equipment according to layout plans, blueprints, or other drawings.</t>
+  </si>
+  <si>
+    <t>Align machines or equipment, using hoists, jacks, hand tools, squares, rules, micrometers, lasers, or plumb bobs. | Assemble and install equipment, using hand tools and power tools. | Assemble machines, and bolt, weld, rivet, or otherwise fasten them to foundation or other structures, using hand tools and power tools. | Attach moving parts and subassemblies to basic assembly unit, using hand tools and power tools. | Bolt parts, such as side and deck plates, jaw plates, and journals, to basic assembly unit. | Conduct preventative maintenance and repair, and lubricate machines and equipment. | Connect power unit to machines or steam piping to equipment, and test unit to evaluate its mechanical operation. | Construct foundation for machines, using hand tools and building materials such as wood, cement, and steel. | Dismantle machinery and equipment for shipment to installation site, performing installation and maintenance work as part of team. | Dismantle machines, using hammers, wrenches, crowbars, and other hand tools. | Fabricate and dismantle parts, equipment, and machines, using a cutting torch or other cutting equipment. | Insert shims, adjust tension on nuts and bolts, or position parts, using hand tools and measuring instruments, to set specified clearances between moving and stationary parts. | Install robot and modify its program, using teach pendant. | Lay out mounting holes, using measuring instruments, and drill holes with power drill. | Level bedplate and establish centerline, using straightedge, levels, and transit. | Move machinery and equipment, using hoists, dollies, rollers, and trucks. | Operate engine lathe to grind, file, and turn machine parts to dimensional specifications. | Position steel beams to support bedplates of machines and equipment, using blueprints and schematic drawings to determine work procedures. | Replace defective parts of machine, or adjust clearances and alignment of moving parts. | Shrink-fit bushings, sleeves, rings, liners, gears, and wheels to specified items, using portable gas heating equipment. | Signal crane operator to lower basic assembly units to bedplate, and align unit to centerline. | Troubleshoot equipment, electrical components, hydraulics, or other mechanical systems. | Weld, repair, and fabricate equipment or machinery.</t>
+  </si>
+  <si>
+    <t>49-9045.00</t>
+  </si>
+  <si>
+    <t>Refractory Materials Repairers, Except Brickmasons</t>
+  </si>
+  <si>
+    <t>Cell Reliner | Cupola Repairer | Furnace Repairer | Hot Repairman | Ladle Liner | Ladle Repairman | Refractory Bricklayer | Refractory Technician | Refractory Worker</t>
+  </si>
+  <si>
+    <t>Maintenance management software | Microsoft Access | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Time tracking software</t>
+  </si>
+  <si>
+    <t>Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Extent Flexibility | Multilimb Coordination | Control Precision | Oral Comprehension | Manual Dexterity | Trunk Strength | Gross Body Equilibrium | Selective Attention | Problem Sensitivity | Oral Expression | Inductive Reasoning | Deductive Reasoning | Finger Dexterity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Indoors, Not Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Time Pressure | Spend Time Bending or Twisting Your Body | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Hazardous Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Conditions | Spend Time Standing | Exposed to Minor Burns, Cuts, Bites, or Stings | Health and Safety of Other Workers | Contact With Others | Physical Proximity | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Exposed to High Places | Spend Time Walking or Running | In an Open Vehicle or Operating Equipment | Freedom to Make Decisions | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Boilermakers | Brickmasons and Blockmasons | Cement Masons and Concrete Finishers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Fiberglass Laminators and Fabricators | Foundry Mold and Coremakers | Grinding and Polishing Workers, Hand | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Insulation Workers, Floor, Ceiling, and Wall | Maintenance Workers, Machinery | Metal-Refining Furnace Operators and Tenders | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Pourers and Casters, Metal | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Terrazzo Workers and Finishers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Build or repair equipment such as furnaces, kilns, cupolas, boilers, converters, ladles, soaking pits, and ovens, using refractory materials.</t>
+  </si>
+  <si>
+    <t>Chip slag from linings of ladles or remove linings when beyond repair, using hammers and chisels. | Climb scaffolding, carrying hoses, and spray surfaces of cupolas with refractory mixtures, using spray equipment. | Dry and bake new linings by placing inverted linings over burners, building fires in ladles, or by using blowtorches. | Dump and tamp clay in molds, using tamping tools. | Measure furnace walls to determine dimensions and cut required number of sheets from plastic block, using saws. | Mix specified amounts of sand, clay, mortar powder, and water to form refractory clay or mortar, using shovels or mixing machines. | Reline or repair ladles and pouring spouts with refractory clay, using trowels. | Remove worn or damaged plastic block refractory linings of furnaces, using hand tools. | Spread mortar on stopper heads and rods, using trowels, and slide brick sleeves over rods to form refractory jackets. | Transfer clay structures to curing ovens, melting tanks, and drawing kilns, using forklifts.</t>
+  </si>
+  <si>
+    <t>49-9051.00</t>
+  </si>
+  <si>
+    <t>Electrical Power-Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Class Gloving Electrical Lineman | Class Rubber Gloving Lineman | Electrical Lineman | Electrical Lineworker | Lineworker | Power Lineman | Power Lineman Technician | Service Man | Third Step Lineman | Troubleman</t>
+  </si>
+  <si>
+    <t>Bentley MicroStation | Computer aided design and drafting CADD software | Email software | Geographic information system GIS systems | Global positioning system GPS software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Zoom</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Reading Comprehension | Active Learning</t>
+  </si>
+  <si>
+    <t>Building and Construction | English Language | Education and Training | Public Safety and Security | Transportation | Mechanical | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Arm-Hand Steadiness | Multilimb Coordination | Near Vision | Deductive Reasoning | Control Precision | Oral Comprehension | Information Ordering | Manual Dexterity | Finger Dexterity | Inductive Reasoning | Far Vision | Gross Body Equilibrium | Extent Flexibility | Stamina | Trunk Strength | Static Strength | Reaction Time | Response Orientation | Visualization | Flexibility of Closure | Rate Control | Selective Attention | Perceptual Speed | Category Flexibility | Oral Expression | Speech Recognition | Depth Perception | Visual Color Discrimination | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Exposed to High Places | Frequency of Decision Making | Exposed to Hazardous Equipment | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Importance of Being Exact or Accurate | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Extremely Bright or Inadequate Lighting Conditions | Telephone Conversations | Work Outcomes and Results of Other Workers | In an Open Vehicle or Operating Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Spend Time Standing | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Consequence of Error | Determine Tasks, Priorities and Goals | Indoors, Not Environmentally Controlled | E-Mail | Exposed to Contaminants | Deal With External Customers or the Public in General | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electricians | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Hoist and Winch Operators | Operating Engineers and Other Construction Equipment Operators | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Power Distributors and Dispatchers | Rail-Track Laying and Maintenance Equipment Operators | Riggers | Signal and Track Switch Repairers | Structural Iron and Steel Workers | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Install or repair cables or wires used in electrical power or distribution systems. May erect poles and light or heavy duty transmission towers.</t>
+  </si>
+  <si>
+    <t>Adhere to safety practices and procedures, such as checking equipment regularly and erecting barriers around work areas. | Attach cross-arms, insulators, and auxiliary equipment to poles prior to installing them. | Clean, tin, and splice corresponding conductors by twisting ends together or by joining ends with metal clamps and soldering connections. | Climb poles or use truck-mounted buckets to access equipment. | Coordinate work assignment preparation and completion with other workers. | Cut and peel lead sheathing and insulation from defective or newly installed cables and conduits prior to splicing. | Cut trenches for laying underground cables, using trenchers and cable plows. | Dig holes, using augers, and set poles, using cranes and power equipment. | Drive vehicles equipped with tools and materials to job sites. | Identify defective sectionalizing devices, circuit breakers, fuses, voltage regulators, transformers, switches, relays, or wiring, using wiring diagrams and electrical-testing instruments. | Inspect and test power lines and auxiliary equipment to locate and identify problems, using reading and testing instruments. | Install watt-hour meters and connect service drops between power lines and consumers' facilities. | Install, maintain, and repair electrical distribution and transmission systems, including conduits, cables, wires, and related equipment, such as transformers, circuit breakers, and switches. | Lay underground cable directly in trenches, or string it through conduit running through the trenches. | Open switches or attach grounding devices to remove electrical hazards from disturbed or fallen lines or to facilitate repairs. | Place insulating or fireproofing materials over conductors and joints. | Pull up cable by hand from large reels mounted on trucks. | Replace or straighten damaged poles. | Splice or solder cables together or to overhead transmission lines, customer service lines, or street light lines, using hand tools, epoxies, or specialized equipment. | String wire conductors and cables between poles, towers, trenches, pylons, and buildings, setting lines in place and using winches to adjust tension. | Test conductors, according to electrical diagrams and specifications, to identify corresponding conductors and to prevent incorrect connections. | Travel in trucks, helicopters, and airplanes to inspect lines for freedom from obstruction and adequacy of insulation. | Trim trees that could be hazardous to the functioning of cables or wires.</t>
+  </si>
+  <si>
+    <t>49-9052.00</t>
+  </si>
+  <si>
+    <t>Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Cable Splicer | Cable Technician | Cable Television Technician (Cable TV Tech) | Combination Technician | Field Service Technician | Installation and Repair Technician (I and R Technician) | Installer | Lineman | Outside Plant Technician | Service Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Cisco IOS | Email software | Mapcom systems M4 | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Ping tools | Slack | Voice over internet protocol VoIP system software | Web browser software | Workforce management system software</t>
+  </si>
+  <si>
+    <t>Speaking | Critical Thinking | Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Telecommunications | Customer and Personal Service | English Language | Public Safety and Security | Computers and Electronics | Mechanical | Education and Training | Communications and Media</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Extent Flexibility | Arm-Hand Steadiness | Problem Sensitivity | Manual Dexterity | Multilimb Coordination | Trunk Strength | Information Ordering | Deductive Reasoning | Selective Attention | Visualization | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Written Comprehension | Speech Clarity | Far Vision | Static Strength | Control Precision | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Telephone Conversations | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Very Hot or Cold Temperatures | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Exposed to High Places | Deal With External Customers or the Public in General | Spend Time Standing | Exposed to Cramped Work Space, Awkward Positions | Spend Time Making Repetitive Motions | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Hazardous Conditions | Indoors, Environmentally Controlled | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Outdoors, Under Cover | Importance of Repeating Same Tasks | Spend Time Bending or Twisting Your Body | Physical Proximity</t>
+  </si>
+  <si>
+    <t>Audiovisual Equipment Installers and Repairers | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electricians | Electronic Equipment Installers and Repairers, Motor Vehicles | Helpers--Electricians | Hoist and Winch Operators | Lighting Technicians | Pipelayers | Power Distributors and Dispatchers | Radio, Cellular, and Tower Equipment Installers and Repairers | Security and Fire Alarm Systems Installers | Signal and Track Switch Repairers | Telecommunications Engineering Specialists | Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Install and repair telecommunications cable, including fiber optics.</t>
+  </si>
+  <si>
+    <t>Access specific areas to string lines, or install terminal boxes, auxiliary equipment, or appliances, using bucket trucks, climbing poles or ladders, or entering tunnels, trenches, or crawl spaces. | Clean or maintain tools or test equipment. | Compute impedance of wires from poles to houses to determine additional resistance needed for reducing signals to desired levels. | Dig holes for power poles, using power augers or shovels, set poles in place with cranes, and hoist poles upright, using winches. | Dig trenches for underground wires or cables. | Explain cable service to subscribers after installation, and collect any installation fees due. | Fill and tamp holes, using cement, earth, and tamping devices. | Inspect or test lines or cables, recording and analyzing test results, to assess transmission characteristics and locate faults or malfunctions. | Install equipment such as amplifiers or repeaters to maintain the strength of communications transmissions. | Lay underground cable directly in trenches, or string it through conduits running through trenches. | Measure signal strength at utility poles, using electronic test equipment. | Place insulation over conductors, or seal splices with moisture-proof covering. | Pull cable through ducts by hand or with winches. | Pull up cable by hand from large reels mounted on trucks. | Set up service for customers, installing, connecting, testing, or adjusting equipment. | Splice cables, using hand tools, epoxy, or mechanical equipment. | String cables between structures and lines from poles, towers, or trenches, and pull lines to proper tension. | Travel to customers' premises to install, maintain, or repair audio and visual electronic reception equipment or accessories. | Use a variety of construction equipment to complete installations, such as digger derricks, trenchers, or cable plows.</t>
+  </si>
+  <si>
+    <t>49-9061.00</t>
+  </si>
+  <si>
+    <t>Camera and Photographic Equipment Repairers</t>
+  </si>
+  <si>
+    <t>Camera Repair Technician | Camera Repairman | Camera Technician | Photo Equipment Technician | Photo Technologist | Photographic Equipment Repair Technician | Photographic Equipment Technician | Photographic Technician (Photo Tech) | Repair Technician | Repairman</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Microsoft Office software | Microsoft Word | RepairTRAX | Statistical process control SPC software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Active Listening | Active Learning | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Computers and Electronics | Customer and Personal Service | English Language | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Visualization | Finger Dexterity | Arm-Hand Steadiness | Problem Sensitivity | Written Comprehension | Manual Dexterity | Selective Attention | Information Ordering | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Speech Recognition | Visual Color Discrimination | Far Vision | Control Precision | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Sitting | E-Mail | Telephone Conversations | Time Pressure</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Audiovisual Equipment Installers and Repairers | Avionics Technicians | Calibration Technologists and Technicians | Computer, Automated Teller, and Office Machine Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Electronic Equipment Installers and Repairers, Motor Vehicles | Lighting Technicians | Medical Equipment Repairers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Motion Picture Projectionists | Ophthalmic Laboratory Technicians | Photographic Process Workers and Processing Machine Operators | Photonics Technicians | Prepress Technicians and Workers | Timing Device Assemblers and Adjusters</t>
+  </si>
+  <si>
+    <t>Repair and adjust cameras and photographic equipment, including commercial video and motion picture camera equipment.</t>
+  </si>
+  <si>
+    <t>Adjust cameras, photographic mechanisms, or equipment such as range and view finders, shutters, light meters, or lens systems, using hand tools. | Assemble aircraft cameras, still or motion picture cameras, photographic equipment, or frames, using diagrams, blueprints, bench machines, hand tools, or power tools. | Calibrate and verify accuracy of light meters, shutter diaphragm operation, or lens carriers, using timing instruments. | Clean and lubricate cameras and polish camera lenses, using cleaning materials and work aids. | Disassemble equipment to gain access to defect, using hand tools. | Examine cameras, equipment, processed film, or laboratory reports to diagnose malfunction, using work aids and specifications. | Fabricate or modify defective electronic, electrical, or mechanical components, using bench lathe, milling machine, shaper, grinder, or precision hand tools, according to specifications. | Install electrical assemblies and wiring in aircraft camera housings and memory cards or film in cameras, following blueprints and using hand tools and soldering equipment. | Lay out reference points and dimensions on parts or metal stock to be machined, using precision measuring instruments. | Measure parts to verify specified dimensions or settings, such as camera shutter speed or light meter reading accuracy, using measuring instruments. | Read and interpret engineering drawings, diagrams, instructions, or specifications to determine needed repairs, fabrication method, and operation sequence. | Recommend design changes or upgrades of microfilming, film-developing, or photographic equipment. | Record test data and document fabrication techniques on reports. | Requisition parts or materials. | Test equipment performance, focus of lens system, diaphragm alignment, lens mounts, or film transport, using precision gauges.</t>
+  </si>
+  <si>
+    <t>49-9062.00</t>
+  </si>
+  <si>
+    <t>Medical Equipment Repairers</t>
+  </si>
+  <si>
+    <t>Biomedical Electronics Technician (Biomed Electronics Tech) | Biomedical Engineering Technician (Biomed Engineering Tech) | Biomedical Equipment Technician (BMET) | Biomedical Technician (Biomed Tech) | Dental Equipment Technician (Dental Equipment Tech) | Durable Medical Equipment Technician (DME Tech) | Medical Equipment Service Tech (Medical Equipment Service Technician) | Repair Technician (Repair Tech) | Service Technician (Service Tech) | X-ray Service Engineer</t>
+  </si>
+  <si>
+    <t>Computerized maintenance management system CMMS | FaceTime | Inventory control system software | Medical equipment diagnostic software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software | Salesforce software | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Learning | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Computers and Electronics | Customer and Personal Service | English Language | Engineering and Technology | Mathematics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Finger Dexterity | Deductive Reasoning | Written Comprehension | Inductive Reasoning | Information Ordering | Visualization | Arm-Hand Steadiness | Manual Dexterity | Visual Color Discrimination | Control Precision | Oral Comprehension | Written Expression | Oral Expression | Speech Clarity | Speech Recognition | Extent Flexibility | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | E-Mail | Telephone Conversations | Contact With Others | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Deal With External Customers or the Public in General | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Coordinate or Lead Others in Accomplishing Work Activities | In an Enclosed Vehicle or Operate Enclosed Equipment | Physical Proximity | Spend Time Standing | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering and Operations Technologists and Technicians | Automotive Engineering Technicians | Avionics Technicians | Bioengineers and Biomedical Engineers | Calibration Technologists and Technicians | Computer, Automated Teller, and Office Machine Repairers | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Industrial Engineering Technologists and Technicians | Industrial Machinery Mechanics | Maintenance and Repair Workers, General | Mechanical Engineering Technologists and Technicians | Medical Appliance Technicians | Medical Equipment Preparers | Nanotechnology Engineering Technologists and Technicians | Photonics Technicians | Robotics Technicians</t>
+  </si>
+  <si>
+    <t>Test, adjust, or repair biomedical or electromedical equipment.</t>
+  </si>
+  <si>
+    <t>Compute power and space requirements for installing medical, dental, or related equipment and install units to manufacturers' specifications. | Contribute expertise to develop medical maintenance standard operating procedures. | Disassemble malfunctioning equipment and remove, repair, or replace defective parts, such as motors, clutches, or transformers. | Evaluate technical specifications to identify equipment or systems best suited for intended use and possible purchase, based on specifications, user needs, or technical requirements. | Examine medical equipment or facility's structural environment and check for proper use of equipment to protect patients and staff from electrical or mechanical hazards and to ensure compliance with safety regulations. | Explain or demonstrate correct operation or preventive maintenance of medical equipment to personnel. | Fabricate, dress down, or substitute parts or major new items to modify equipment to meet unique operational or research needs, working from job orders, sketches, modification orders, samples, or discussions with operating officials. | Inspect, test, or troubleshoot malfunctioning medical or related equipment, following manufacturers' specifications and using test and analysis instruments. | Install medical equipment. | Keep records of maintenance, repair, and required updates of equipment. | Make computations relating to load requirements of wiring or equipment, using algebraic expressions and standard formulas. | Perform preventive maintenance or service, such as cleaning, lubricating, or adjusting equipment. | Plan and carry out work assignments, using blueprints, schematic drawings, technical manuals, wiring diagrams, or liquid or air flow sheets, following prescribed regulations, directives, or other instructions as required. | Repair shop equipment, metal furniture, or hospital equipment, including welding broken parts or replacing missing parts, or bring item into local shop for major repairs. | Research catalogs or repair part lists to locate sources for repair parts, requisitioning parts and recording their receipt. | Solder loose connections, using soldering iron. | Study technical manuals or attend training sessions provided by equipment manufacturers to maintain current knowledge. | Supervise or advise subordinate personnel. | Test or calibrate components or equipment, following manufacturers' manuals and troubleshooting techniques, using hand tools, power tools, or measuring devices. | Test, evaluate, and classify excess or in-use medical equipment and determine serviceability, condition, and disposition, in accordance with regulations.</t>
+  </si>
+  <si>
+    <t>49-9063.00</t>
+  </si>
+  <si>
+    <t>Musical Instrument Repairers and Tuners</t>
+  </si>
+  <si>
+    <t>Brass Instrument Repair Technician (Brass Instrument Repair Tech) | Fretted String Instrument Repairer | Guitar Repairer | Instrument Repair Technician (Instrument Repair Tech) | Luthier | Musical Instrument Repair Technician (Musical Instrument Repair Tech) | Piano Technician (Piano Tech) | Piano Tuner | Stringed Instrument Repairer | Woodwind Instrument Technician (Woodwind Instrument Tech)</t>
+  </si>
+  <si>
+    <t>Katsura Shareware KS Strobe Tuner | Katsura Shareware ProLevel | Katsura Shareware SoundFrames | Mensurix Audio | Reyburn CyberTuner | TonalEnergy Tuner &amp; Metronome | Tunable Instrument Tuner | TuneLab | Tunic OnlyPure | Veritune Verituner</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mechanical | Fine Arts | English Language</t>
+  </si>
+  <si>
+    <t>Hearing Sensitivity | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Near Vision | Control Precision | Auditory Attention | Visualization | Problem Sensitivity | Deductive Reasoning | Flexibility of Closure | Inductive Reasoning | Selective Attention | Category Flexibility | Information Ordering | Oral Comprehension | Oral Expression | Written Comprehension | Far Vision | Multilimb Coordination | Speed of Closure</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | E-Mail | Indoors, Environmentally Controlled | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Deal With External Customers or the Public in General | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Camera and Photographic Equipment Repairers | Coil Winders, Tapers, and Finishers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Jewelers and Precious Stone and Metal Workers | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Sheet Metal Workers | Timing Device Assemblers and Adjusters | Tool Grinders, Filers, and Sharpeners | Watch and Clock Repairers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Repair percussion, stringed, reed, or wind instruments. May specialize in one area, such as piano tuning.</t>
+  </si>
+  <si>
+    <t>Adjust felt hammers on pianos to increase tonal mellowness or brilliance, using sanding paddles, lacquer, or needles. | Adjust string tensions to tune instruments, using hand tools and electronic tuning devices. | Align pads and keys on reed or wind instruments. | Assemble and install new pipe organs and pianos in buildings. | Compare instrument pitches with tuning tool pitches to tune instruments. | Deliver pianos to purchasers or to locations of their use. | Disassemble instruments and parts for repair and adjustment. | Inspect instruments to locate defects, and to determine their value or the level of restoration required. | Make wood replacement parts, using woodworking machines and hand tools. | Mix and measure glue that will be used for instrument repair. | Play instruments to evaluate their sound quality and to locate any defects. | Polish instruments, using rags and polishing compounds, buffing wheels, or burnishing tools. | Reassemble instruments following repair, using hand tools and power tools and glue, hair, yarn, resin, or clamps, and lubricate instruments as necessary. | Refinish and polish piano cabinets or cases to prepare them for sale. | Refinish instruments to protect and decorate them, using hand tools, buffing tools, and varnish. | Remove dents and burrs from metal instruments, using mallets and burnishing tools. | Remove irregularities from tuning pins, strings, and hammers of pianos, using wood blocks or filing tools. | Repair cracks in wood or metal instruments, using pinning wire, lathes, fillers, clamps, or soldering irons. | Repair or replace musical instrument parts and components, such as strings, bridges, felts, and keys, using hand and power tools. | Shape old parts and replacement parts to improve tone or intonation, using hand tools, lathes, or soldering irons. | Solder posts and parts to hold them in their proper places. | Strike wood, fiberglass, or metal bars of instruments, and use tuned blocks, stroboscopes, or electronic tuners to evaluate tones made by instruments. | String instruments, and adjust trusses and bridges of instruments to obtain specified string tensions and heights. | Wash metal instruments in lacquer-stripping and cyanide solutions to remove lacquer and tarnish.</t>
+  </si>
+  <si>
+    <t>49-9064.00</t>
+  </si>
+  <si>
+    <t>Watch and Clock Repairers</t>
+  </si>
+  <si>
+    <t>Antique Clock Repairer | Clock Repair Technician | Clock Repairer | Watch Estimator | Watch Repair Person | Watch Repair Technician | Watch Repairer | Watch Technician (Watch Tech) | Watch and Clock Repairer</t>
+  </si>
+  <si>
+    <t>GrenSoft WorkTracer | IBM Lotus Notes | Intuit QuickBooks | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software | Sage Software Sage50 | Upland Consulting Group Repair Traq | WatchWare Repair Shop</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Mechanical | Administrative | Engineering and Technology | Production and Processing</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Arm-Hand Steadiness | Control Precision | Near Vision | Manual Dexterity | Information Ordering | Problem Sensitivity | Visualization | Category Flexibility | Oral Expression | Written Comprehension | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Sitting | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Time Pressure | Contact With Others | Physical Proximity | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Camera and Photographic Equipment Repairers | Coil Winders, Tapers, and Finishers | Coin, Vending, and Amusement Machine Servicers and Repairers | Cutting and Slicing Machine Setters, Operators, and Tenders | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Jewelers and Precious Stone and Metal Workers | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Musical Instrument Repairers and Tuners | Paper Goods Machine Setters, Operators, and Tenders | Textile Winding, Twisting, and Drawing Out Machine Setters, Operators, and Tenders | Timing Device Assemblers and Adjusters | Tool Grinders, Filers, and Sharpeners</t>
+  </si>
+  <si>
+    <t>Repair, clean, and adjust mechanisms of timing instruments, such as watches and clocks. Includes watchmakers, watch technicians, and mechanical timepiece repairers.</t>
+  </si>
+  <si>
+    <t>Adjust timing regulators, using truing calipers, watch-rate recorders, and tweezers. | Clean, rinse, and dry timepiece parts, using solutions and ultrasonic or mechanical watch-cleaning machines. | Demagnetize mechanisms, using demagnetizing machines. | Disassemble timepieces and inspect them for defective, worn, misaligned, or rusty parts, using loupes. | Estimate repair costs and timepiece values. | Fabricate parts for watches and clocks, using small lathes and other machines. | Gather information from customers about a timepiece's problems and its service history. | Oil moving parts of timepieces. | Order supplies, including replacement parts, for timing instruments. | Perform regular adjustment and maintenance on timepieces, watch cases, and watch bands. | Reassemble timepieces, replacing glass faces and batteries, before returning them to customers. | Record quantities and types of timepieces repaired, serial and model numbers of items, work performed, and charges for repairs. | Repair or replace broken, damaged, or worn parts on timepieces, using lathes, drill presses, and hand tools. | Test and replace batteries and other electronic components. | Test timepiece accuracy and performance, using meters and other electronic instruments.</t>
+  </si>
+  <si>
+    <t>49-9069.00</t>
+  </si>
+  <si>
+    <t>Precision Instrument and Equipment Repairers, All Other</t>
+  </si>
+  <si>
+    <t>Calibration Repairer | Instrument Repairer | Instrument Technician | Laboratory Instrument Repairer | Meter Repairer | Precision Instrument Repairer | Scale Technician | Scientific Instrument Repairer | Test Equipment Repairer | Optical Instrument Repairer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | ANSYS simulation software | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | Three-dimensional 3D computer aided design CAD software | Two-dimensional 2D computer aided design CAD software | Email software | Microsoft PowerPoint | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Mechanical | Computers and Electronics | Engineering and Technology | Mathematics | English Language | Physics | Design | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Importance of Being Exact or Accurate | Consequence of Error | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Camera and Photographic Equipment Repairers | Medical Equipment Repairers | Musical Instrument Repairers and Tuners | Watch and Clock Repairers | Calibration Technologists and Technicians | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electric Motor, Power Tool, and Related Repairers | Control and Valve Installers and Repairers, Except Mechanical Door | Avionics Technicians | Computer, Automated Teller, and Office Machine Repairers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Locksmiths and Safe Repairers | Electrical and Electronic Engineering Technologists and Technicians | Mechanical Engineering Technologists and Technicians | Engineering Technologists and Technicians, Except Drafters, All Other | First-Line Supervisors of Mechanics, Installers, and Repairers | Installation, Maintenance, and Repair Workers, All Other | Inspectors, Testers, Sorters, Samplers, and Weighers | Ophthalmic Laboratory Technicians</t>
+  </si>
+  <si>
+    <t>All precision instrument and equipment repairers not listed separately.</t>
+  </si>
+  <si>
+    <t>Repair and calibrate precision instruments in specialties not classified separately. | Diagnose malfunctions using test equipment, schematics, and technical manuals. | Disassemble instruments and inspect components for wear, damage, or contamination. | Replace, adjust, and align mechanical, optical, and electronic parts. | Calibrate instruments to manufacturer specifications and traceable standards. | Test repaired instruments to verify accuracy, precision, and performance. | Clean, lubricate, and perform preventive maintenance on instruments. | Fabricate or modify small parts and fixtures when replacements are unavailable. | Maintain calibration certificates, service records, and traceability documentation. | Advise customers on instrument care, operation, and repair options. | Estimate repair costs, turnaround times, and parts requirements. | Order and stock replacement parts, tools, and calibration standards. | Follow electrostatic discharge, cleanliness, and safety procedures. | Keep current with new instrument technologies and repair techniques.</t>
+  </si>
+  <si>
+    <t>49-9071.00</t>
+  </si>
+  <si>
+    <t>Maintenance and Repair Workers, General</t>
+  </si>
+  <si>
+    <t>Building Mechanic | Equipment Engineering Technician | Facilities Technician | Maintenance Engineer | Maintenance Journeyman | Maintenance Man | Maintenance Mechanic | Maintenance Specialist | Maintenance Technician | Maintenance Worker</t>
+  </si>
+  <si>
+    <t>Apple macOS | Autodesk AutoCAD | Computer aided design and drafting software CADD | Computerized maintenance management system CMMS | Computerized time management systems | Dassault Systemes CATIA | Data entry software | Database software | Digital direct control DDC energy management software | Dropbox | Eko | FaceTime | Facebook | Google Docs | GroupMe | Handheld computer device software | IBM Notes | Linux | Loom | Microsoft Excel | Microsoft Exchange | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | SAP software | Supervisory control and data acquisition SCADA software | Web browser software | Yardi software | YouTube</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Learning | Monitoring | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Building and Construction | Mathematics | Production and Processing</t>
+  </si>
+  <si>
+    <t>Information Ordering | Arm-Hand Steadiness | Manual Dexterity | Near Vision | Problem Sensitivity | Control Precision | Visualization | Oral Expression | Oral Comprehension | Deductive Reasoning | Finger Dexterity | Multilimb Coordination | Speech Clarity | Speech Recognition | Extent Flexibility | Selective Attention | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Written Expression | Visual Color Discrimination | Far Vision | Gross Body Equilibrium | Gross Body Coordination | Trunk Strength | Static Strength | Perceptual Speed | Written Comprehension | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Telephone Conversations | Health and Safety of Other Workers | E-Mail | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Outdoors, Exposed to All Weather Conditions | Exposed to Hazardous Equipment | Frequency of Decision Making | Exposed to Very Hot or Cold Temperatures | Work Outcomes and Results of Other Workers | Spend Time Standing | Freedom to Make Decisions | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Walking or Running | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Coordinate or Lead Others in Accomplishing Work Activities | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Not Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Indoors, Environmentally Controlled | Time Pressure | Spend Time Bending or Twisting Your Body | Exposed to Minor Burns, Cuts, Bites, or Stings | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Engine and Other Machine Assemblers | Facilities Managers | Farm Equipment Mechanics and Service Technicians | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Hydroelectric Plant Technicians | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Plumbers, Pipefitters, and Steamfitters | Stationary Engineers and Boiler Operators</t>
+  </si>
+  <si>
+    <t>Perform work involving the skills of two or more maintenance or craft occupations to keep machines, mechanical equipment, or the structure of a building in repair. Duties may involve pipe fitting; HVAC maintenance; insulating; welding; machining; carpentry; repairing electrical or mechanical equipment; installing, aligning, and balancing new equipment; and repairing buildings, floors, or stairs.</t>
+  </si>
+  <si>
+    <t>Adjust functional parts of devices or control instruments, using hand tools, levels, plumb bobs, or straightedges. | Align and balance new equipment after installation. | Assemble boilers at installation sites, using tools such as levels, plumb bobs, hammers, torches, or other hand tools. | Assemble, install, or repair wiring, electrical or electronic components, pipe systems, plumbing, machinery, or equipment. | Clean or lubricate shafts, bearings, gears, or other parts of machinery. | Design new equipment to aid in the repair or maintenance of machines, mechanical equipment, or building structures. | Diagnose mechanical problems and determine how to correct them, checking blueprints, repair manuals, or parts catalogs, as necessary. | Dismantle machines, equipment, or devices to access and remove defective parts, using hoists, cranes, hand tools, or power tools. | Estimate costs to repair machinery, equipment, or building structures. | Fabricate or repair counters, benches, partitions, or other wooden structures, such as sheds or outbuildings. | Inspect used parts to determine changes in dimensional requirements, using rules, calipers, micrometers, or other measuring instruments. | Inspect, operate, or test machinery or equipment to diagnose machine malfunctions. | Install equipment to improve the energy or operational efficiency of residential or commercial buildings. | Maintain or repair specialized equipment or machinery located in cafeterias, laundries, hospitals, stores, offices, or factories. | Operate cutting torches or welding equipment to cut or join metal parts. | Order parts, supplies, or equipment from catalogs or suppliers. | Paint or repair roofs, windows, doors, floors, woodwork, plaster, drywall, or other parts of building structures. | Perform general cleaning of buildings or properties. | Perform routine maintenance on boilers, such as replacing burners or hoses, installing replacement parts, or reinforcing structural weaknesses to ensure optimal boiler efficiency. | Perform routine maintenance, such as inspecting drives, motors, or belts, checking fluid levels, replacing filters, or doing other preventive maintenance actions. | Plan and lay out repair work, using diagrams, drawings, blueprints, maintenance manuals, or schematic diagrams. | Position, attach, or blow insulating materials to prevent energy losses from buildings, pipes, or other structures or objects. | Provide groundskeeping services, such as landscaping or snow removal. | Record type and cost of maintenance or repair work. | Repair machines, equipment, or structures, using tools such as hammers, hoists, saws, drills, wrenches, or equipment such as precision measuring instruments or electrical or electronic testing devices. | Set up and operate machine tools to repair or fabricate machine parts, jigs, fixtures, or tools. | Train or manage maintenance personnel or subcontractors.</t>
+  </si>
+  <si>
+    <t>49-9081.00</t>
+  </si>
+  <si>
+    <t>Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Field Service Technician | Renewable Energy Technician | Service Technician | Troubleshooting Technician | Wind Farm Support Specialist | Wind Technician | Wind Turbine Operator | Wind Turbine Service Technician | Wind Turbine Technician | Wind Turbine Troubleshooting Technician</t>
+  </si>
+  <si>
+    <t>Computerized diagnostic software | Computerized maintenance management system CMMS | IBM Maximo Asset Management | Industrial control systems software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Programmable logic controller PLC software | SAP software | Structured query language SQL | Supervisory control and data acquisition SCADA software | Vestas Wind Systems A/S Vestas Remote Panel | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Reading Comprehension | Monitoring | Active Learning | Active Listening | Speaking | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Mechanical | Computers and Electronics | English Language | Public Safety and Security | Engineering and Technology | Education and Training | Administration and Management | Mathematics | Building and Construction | Physics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Comprehension | Finger Dexterity | Near Vision | Arm-Hand Steadiness | Manual Dexterity | Deductive Reasoning | Control Precision | Multilimb Coordination | Written Comprehension | Oral Expression | Inductive Reasoning | Information Ordering | Visualization | Far Vision | Gross Body Equilibrium | Extent Flexibility | Trunk Strength | Dynamic Strength | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility | Speech Clarity | Speech Recognition | Auditory Attention | Stamina | Static Strength | Reaction Time | Written Expression</t>
+  </si>
+  <si>
+    <t>Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to High Places | Exposed to Hazardous Conditions | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Cramped Work Space, Awkward Positions | Indoors, Not Environmentally Controlled | Consequence of Error | Outdoors, Exposed to All Weather Conditions | E-Mail | Contact With Others | Exposed to Very Hot or Cold Temperatures | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Spend Time Bending or Twisting Your Body | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Contaminants | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Physical Proximity | Spend Time Making Repetitive Motions | Outdoors, Under Cover | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Importance of Being Exact or Accurate | Exposed to Extremely Bright or Inadequate Lighting Conditions | Time Pressure | Freedom to Make Decisions | Importance of Repeating Same Tasks | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Work Outcomes and Results of Other Workers | Spend Time Climbing Ladders, Scaffolds, or Poles | Spend Time Keeping or Regaining Balance | Determine Tasks, Priorities and Goals | Spend Time Kneeling, Crouching, Stooping, or Crawling | Level of Competition | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Avionics Technicians | Biomass Plant Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Engineers | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Gas Plant Operators | Geothermal Production Managers | Geothermal Technicians | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Power Distributors and Dispatchers | Power Plant Operators | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Solar Thermal Installers and Technicians | Stationary Engineers and Boiler Operators | Wind Energy Development Managers | Wind Energy Engineers | Wind Energy Operations Managers</t>
+  </si>
+  <si>
+    <t>Inspect, diagnose, adjust, or repair wind turbines. Perform maintenance on wind turbine equipment including resolving electrical, mechanical, and hydraulic malfunctions.</t>
+  </si>
+  <si>
+    <t>Assist in assembly of individual wind generators or construction of wind farms. | Climb wind turbine towers to inspect, maintain, or repair equipment. | Collect turbine data for testing or research and analysis. | Diagnose problems involving wind turbine generators or control systems. | Inspect or repair fiberglass turbine blades. | Maintain tool and spare parts inventories required for repair, installation, or replacement services. | Perform routine maintenance on wind turbine equipment, underground transmission systems, wind fields substations, or fiber optic sensing and control systems. | Start or restart wind turbine generator systems to ensure proper operations. | Test electrical components of wind systems with devices, such as voltage testers, multimeters, oscilloscopes, infrared testers, or fiber optic equipment. | Test structures, controls, or mechanical, hydraulic, or electrical systems, according to test plans or in coordination with engineers. | Train end-users, distributors, installers, or other technicians in wind commissioning, testing, or other technical procedures. | Troubleshoot or repair mechanical, hydraulic, or electrical malfunctions related to variable pitch systems, variable speed control systems, converter systems, or related components.</t>
+  </si>
+  <si>
+    <t>49-9091.00</t>
+  </si>
+  <si>
+    <t>Coin, Vending, and Amusement Machine Servicers and Repairers</t>
+  </si>
+  <si>
+    <t>Cooler Deliverer | Field Service Technician | Fountain Vending Mechanic | Full Service Vending Driver | Refurbish Technician | Service Technician | Slot Technician | Vending Mechanic | Vending Service Technician | Vending Technician</t>
+  </si>
+  <si>
+    <t>Email software | Inventory tracking software | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Mechanical | Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Near Vision | Control Precision | Information Ordering | Multilimb Coordination | Visualization | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Oral Expression | Oral Comprehension | Selective Attention | Written Comprehension</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | E-Mail | Telephone Conversations | Contact With Others | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Determine Tasks, Priorities and Goals | In an Enclosed Vehicle or Operate Enclosed Equipment | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Computer, Automated Teller, and Office Machine Repairers | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Home Appliance Repairers | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Mobile Heavy Equipment Mechanics, Except Engines | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Office Machine Operators, Except Computer | Packaging and Filling Machine Operators and Tenders | Paper Goods Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Watch and Clock Repairers</t>
+  </si>
+  <si>
+    <t>Install, service, adjust, or repair coin, vending, or amusement machines including video games, juke boxes, pinball machines, or slot machines.</t>
+  </si>
+  <si>
+    <t>Adjust and repair coin, vending, or amusement machines and meters and replace defective mechanical and electrical parts, using hand tools, soldering irons, and diagrams. | Adjust machine pressure gauges and thermostats. | Clean and oil machine parts. | Collect coins and bills from machines, prepare invoices, and settle accounts with concessionaires. | Contact other repair personnel or make arrangements for the removal of machines in cases where major repairs are required. | Disassemble and assemble machines, according to specifications and using hand and power tools. | Fill machines with products, ingredients, money, and other supplies. | Inspect machines and meters to determine causes of malfunctions and fix minor problems such as jammed bills or stuck products. | Install machines, making the necessary water and electrical connections in compliance with codes. | Keep records of merchandise distributed and money collected. | Maintain records of machine maintenance and repair. | Make service calls to maintain and repair machines. | Order parts needed for machine repairs. | Record transaction information on forms or logs, and notify designated personnel of discrepancies. | Refer to manuals and wiring diagrams to gather information needed to repair machines. | Replace malfunctioning parts, such as worn magnetic heads on automatic teller machine (ATM) card readers. | Test machines to determine proper functioning. | Transport machines to installation sites.</t>
+  </si>
+  <si>
+    <t>49-9092.00</t>
+  </si>
+  <si>
+    <t>Commercial Divers</t>
+  </si>
+  <si>
+    <t>Commercial Diver | Diver | Diver Tender | Hard Hat Diver | Non Destructive Testing Under Water Welder (NDT U/W Welder) | Salvage Diver | Tender</t>
+  </si>
+  <si>
+    <t>Diving logbook software | Diving table software | Dynamic positioning DP software | Remote operated vehicle ROV dive log software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Reading Comprehension | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Physics | Customer and Personal Service | Mathematics | Public Safety and Security | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Arm-Hand Steadiness | Control Precision | Multilimb Coordination | Manual Dexterity | Finger Dexterity | Near Vision | Speech Recognition | Deductive Reasoning | Information Ordering | Inductive Reasoning | Extent Flexibility | Perceptual Speed | Written Comprehension | Flexibility of Closure | Static Strength | Far Vision | Depth Perception | Speech Clarity | Visual Color Discrimination | Stamina | Trunk Strength | Reaction Time | Time Sharing | Selective Attention | Visualization | Category Flexibility | Dynamic Strength | Response Orientation | Spatial Orientation | Originality | Fluency of Ideas | Written Expression | Gross Body Equilibrium | Gross Body Coordination</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Freedom to Make Decisions | Importance of Being Exact or Accurate | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work Outcomes and Results of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Telephone Conversations | Determine Tasks, Priorities and Goals | Physical Proximity | Consequence of Error | Impact of Decisions on Co-workers or Company Results | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure | Exposed to Contaminants | Spend Time Standing | Indoors, Not Environmentally Controlled | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Boilermakers | Construction Laborers | Dredge Operators | Earth Drillers, Except Oil and Gas | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Electricians | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Hoist and Winch Operators | Marine Engineers and Naval Architects | Mobile Heavy Equipment Mechanics, Except Engines | Operating Engineers and Other Construction Equipment Operators | Pipelayers | Plumbers, Pipefitters, and Steamfitters | Riggers | Rotary Drill Operators, Oil and Gas | Roustabouts, Oil and Gas | Sailors and Marine Oilers | Septic Tank Servicers and Sewer Pipe Cleaners | Ship Engineers | Welders, Cutters, Solderers, and Brazers</t>
+  </si>
+  <si>
+    <t>Work below surface of water, using surface-supplied air or scuba equipment to inspect, repair, remove, or install equipment and structures. May use a variety of power and hand tools, such as drills, sledgehammers, torches, and welding equipment. May conduct tests or experiments, rig explosives, or photograph structures or marine life.</t>
+  </si>
+  <si>
+    <t>Carry out non-destructive testing, such as tests for cracks on the legs of oil rigs at sea. | Check and maintain diving equipment, such as helmets, masks, air tanks, harnesses, or gauges. | Communicate with workers on the surface while underwater, using signal lines or telephones. | Cut and weld steel, using underwater welding equipment, jigs, and supports. | Descend into water with the aid of diver helpers, using scuba gear or diving suits. | Drill holes in rock and rig explosives for underwater demolitions. | Inspect and test docks, ships, buoyage systems, plant intakes or outflows, or underwater pipelines, cables, or sewers, using closed circuit television, still photography, and testing equipment. | Inspect the condition of underwater steel or wood structures. | Install pilings or footings for piers or bridges. | Install, inspect, clean, or repair piping or valves. | Obtain information about diving tasks and environmental conditions. | Operate underwater video, sonar, recording, or related equipment to investigate underwater structures or marine life. | Perform activities related to underwater search and rescue, salvage, recovery, or cleanup operations. | Perform offshore oil or gas exploration or extraction duties, such as conducting underwater surveys or repairing and maintaining drilling rigs or platforms. | Recover objects by placing rigging around sunken objects, hooking rigging to crane lines, and operating winches, derricks, or cranes to raise objects. | Remove obstructions from strainers or marine railway or launching ways, using pneumatic or power hand tools. | Remove rubbish or pollution from the sea. | Repair ships, bridge foundations, or other structures below the water line, using caulk, bolts, and hand tools. | Salvage wrecked ships or their cargo, using pneumatic power velocity and hydraulic tools and explosive charges, when necessary. | Set or guide placement of pilings or sandbags to provide support for structures, such as docks, bridges, cofferdams, or platforms. | Supervise or train other divers, including hobby divers. | Take appropriate safety precautions, such as monitoring dive lengths and depths and registering with authorities before diving expeditions begin. | Take test samples or photographs to assess the condition of vessels or structures.</t>
+  </si>
+  <si>
+    <t>49-9094.00</t>
+  </si>
+  <si>
+    <t>Locksmiths and Safe Repairers</t>
+  </si>
+  <si>
+    <t>CML (Certified Master Locksmith) | CMS (Certified Master Safecracker) | Certified Professional Safe Technician (CPS) | Forensic Locksmith | Lock Technician (Lock Tech) | Locksmith | RST (Registered Safe Technician) | Road Service Locksmith | Safe Technician (Safe Tech) | Vault Technician (Vault Tech)</t>
+  </si>
+  <si>
+    <t>Intuit QuickBooks | Inventory tracking software | Mapping software | Marathon Data Systems ServiceCEO | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Scheduling software | WH Software InstaCode | WH Software MasterKey | dESCO ESC</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Customer and Personal Service | Public Safety and Security | English Language | Administration and Management | Law and Government | Sales and Marketing | Education and Training | Mathematics | Computers and Electronics | Administrative | Economics and Accounting | Building and Construction</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Finger Dexterity | Visualization | Control Precision | Oral Expression | Manual Dexterity | Information Ordering | Deductive Reasoning | Problem Sensitivity | Oral Comprehension | Inductive Reasoning | Written Expression | Selective Attention | Perceptual Speed | Flexibility of Closure | Written Comprehension | Speech Clarity | Speech Recognition | Extent Flexibility | Trunk Strength | Multilimb Coordination</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | E-Mail | Contact With Others | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Frequency of Decision Making | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Not Environmentally Controlled | Time Pressure | Written Letters and Memos | Outdoors, Under Cover | Impact of Decisions on Co-workers or Company Results | Level of Competition | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Automotive Glass Installers and Repairers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electricians | Electronic Equipment Installers and Repairers, Motor Vehicles | Elevator and Escalator Installers and Repairers | Engine and Other Machine Assemblers | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Home Appliance Repairers | Maintenance and Repair Workers, General | Mechanical Door Repairers | Millwrights | Plumbers, Pipefitters, and Steamfitters | Riggers | Security and Fire Alarm Systems Installers | Timing Device Assemblers and Adjusters</t>
+  </si>
+  <si>
+    <t>Repair and open locks, make keys, change locks and safe combinations, and install and repair safes.</t>
+  </si>
+  <si>
+    <t>Cut new or duplicate keys, using impressions or code key machines. | Cut new or duplicate keys, using key cutting machines. | Disassemble mechanical or electrical locking devices, and repair or replace worn tumblers, springs, and other parts, using hand tools. | Insert new or repaired tumblers into locks to change combinations. | Install alarm and electronic access systems. | Install door hardware, such as locks and closers. | Install safes, vault doors, and deposit boxes according to blueprints, using equipment such as power drills, taps, dies, truck cranes, and dollies. | Keep records of company locks and keys. | Move picklocks in cylinders to open door locks without keys. | Open safe locks by drilling. | Remove interior and exterior finishes on safes and vaults, and spray on new finishes. | Repair and adjust safes, vault doors, and vault components, using hand tools, lathes, drill presses, and welding and acetylene cutting apparatus. | Set up and maintain master key systems. | Unlock cars and other vehicles.</t>
+  </si>
+  <si>
+    <t>49-9095.00</t>
+  </si>
+  <si>
+    <t>Manufactured Building and Mobile Home Installers</t>
+  </si>
+  <si>
+    <t>Delivery Crew Worker | Mobile Home Installer | Mobile Home Laborer | Mobile Home Set-Up Person | Modular Set Crew Member | Set Up Technician</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Learning Strategies | Active Learning | Active Listening | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Building and Construction | Public Safety and Security | Customer and Personal Service | Design | Transportation | Engineering and Technology | Mathematics | Mechanical | Law and Government | English Language | Education and Training | Production and Processing</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Control Precision | Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Reaction Time | Problem Sensitivity | Visualization | Trunk Strength | Near Vision | Static Strength | Extent Flexibility | Depth Perception | Oral Comprehension | Response Orientation | Stamina | Far Vision | Gross Body Equilibrium | Gross Body Coordination | Speech Recognition | Visual Color Discrimination | Wrist-Finger Speed | Category Flexibility | Information Ordering | Deductive Reasoning | Oral Expression | Selective Attention | Rate Control | Fluency of Ideas | Speech Clarity | Flexibility of Closure | Spatial Orientation | Perceptual Speed | Inductive Reasoning | Speed of Limb Movement | Originality | Time Sharing | Written Expression | Written Comprehension | Auditory Attention | Hearing Sensitivity | Dynamic Strength</t>
+  </si>
+  <si>
+    <t>Exposed to Hazardous Equipment | Spend Time Standing | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Spend Time Making Repetitive Motions | Time Pressure | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Telephone Conversations | Exposed to Very Hot or Cold Temperatures | Exposed to Cramped Work Space, Awkward Positions | Work Outcomes and Results of Other Workers | Physical Proximity | Exposed to Minor Burns, Cuts, Bites, or Stings | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Conflict Situations | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Exposed to Contaminants | Spend Time Climbing Ladders, Scaffolds, or Poles</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Carpenters | Construction Laborers | Drywall and Ceiling Tile Installers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electricians | Engine and Other Machine Assemblers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Industrial Machinery Mechanics | Layout Workers, Metal and Plastic | Maintenance and Repair Workers, General | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Model Makers, Wood | Plumbers, Pipefitters, and Steamfitters | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters</t>
+  </si>
+  <si>
+    <t>Move or install mobile homes or prefabricated buildings.</t>
+  </si>
+  <si>
+    <t>Confer with customers or read work orders to determine the nature and extent of damage to units. | Connect electrical systems to outside power sources and activate switches to test the operation of appliances and light fixtures. | Connect water hoses to inlet pipes of plumbing systems, and test operation of plumbing fixtures. | Inspect, examine, and test the operation of parts or systems to evaluate operating condition and to determine if repairs are needed. | Install, repair, and replace units, fixtures, appliances, and other items and systems in mobile and modular homes, prefabricated buildings, or travel trailers, using hand tools or power tools. | List parts needed, estimate costs, and plan work procedures, using parts lists, technical manuals, and diagrams. | Locate and repair frayed wiring, broken connections, or incorrect wiring, using ohmmeters, soldering irons, tape, and hand tools. | Move and set up mobile homes or prefabricated buildings on owners' lots or at mobile home parks. | Open and close doors, windows, and drawers to test their operation, trimming edges to fit, using jackplanes or drawknives. | Refinish wood surfaces on cabinets, doors, moldings, and floors, using power sanders, putty, spray equipment, brushes, paints, or varnishes. | Remove damaged exterior panels, repair and replace structural frame members, and seal leaks, using hand tools. | Repair leaks in plumbing or gas lines, using caulking compounds and plastic or copper pipe. | Reset hardware, using chisels, mallets, and screwdrivers. | Seal open sides of modular units to prepare them for shipment, using polyethylene sheets, nails, and hammers.</t>
+  </si>
+  <si>
+    <t>49-9096.00</t>
+  </si>
+  <si>
+    <t>Riggers</t>
+  </si>
+  <si>
+    <t>Gantry Rigger | Hand Rigger | Heavy Lift Rigger | Machinery Erector | Machinery Mover | Marine Rigger | Motor Rigger | Rigger | Rigging Fabricator | Ship Rigger</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Autodesk Maya | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Public Safety and Security | Production and Processing | Customer and Personal Service | Administration and Management | Design | English Language | Education and Training | Engineering and Technology | Building and Construction | Mathematics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Depth Perception | Near Vision | Multilimb Coordination | Control Precision | Oral Comprehension | Information Ordering | Trunk Strength | Far Vision | Speech Recognition | Extent Flexibility | Static Strength | Reaction Time | Manual Dexterity | Visualization | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Oral Expression | Written Comprehension | Speech Clarity | Auditory Attention | Gross Body Equilibrium | Gross Body Coordination | Finger Dexterity | Arm-Hand Steadiness | Selective Attention | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Very Hot or Cold Temperatures | Time Pressure | Contact With Others | Outdoors, Exposed to All Weather Conditions | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Hazardous Equipment | Indoors, Not Environmentally Controlled | Telephone Conversations | Exposed to Contaminants | Spend Time Standing | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Freedom to Make Decisions | Consequence of Error | Spend Time Making Repetitive Motions | Exposed to Cramped Work Space, Awkward Positions | Spend Time Bending or Twisting Your Body | Pace Determined by Speed of Equipment | Determine Tasks, Priorities and Goals | Level of Competition | In an Enclosed Vehicle or Operate Enclosed Equipment | Spend Time Walking or Running | Exposed to Extremely Bright or Inadequate Lighting Conditions | Importance of Repeating Same Tasks | Exposed to Minor Burns, Cuts, Bites, or Stings | Conflict Situations | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Crane and Tower Operators | Electrical Power-Line Installers and Repairers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Helpers--Electricians | Helpers--Installation, Maintenance, and Repair Workers | Hoist and Winch Operators | Industrial Machinery Mechanics | Industrial Truck and Tractor Operators | Maintenance Workers, Machinery | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Motorboat Mechanics and Service Technicians | Operating Engineers and Other Construction Equipment Operators | Pile Driver Operators | Roustabouts, Oil and Gas | Structural Iron and Steel Workers | Structural Metal Fabricators and Fitters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up or repair rigging for construction projects, manufacturing plants, logging yards, ships and shipyards, or for the entertainment industry.</t>
+  </si>
+  <si>
+    <t>Align, level, and anchor machinery. | Attach loads to rigging to provide support or prepare them for moving, using hand and power tools. | Attach pulleys and blocks to fixed overhead structures, such as beams, ceilings, and gin pole booms, using bolts and clamps. | Clean and dress machine surfaces and component parts. | Control movement of heavy equipment through narrow openings or confined spaces, using chainfalls, gin poles, gallows frames, and other equipment. | Dismantle and store rigging equipment after use. | Fabricate, set up, and repair rigging, supporting structures, hoists, and pulling gear, using hand and power tools. | Install ground rigging for yarding lines, attaching chokers to logs and to the lines. | Load machines onto trucks to prepare for transportation. | Manipulate rigging lines, hoists, and pulling gear to move or support materials, such as heavy equipment, ships, or theatrical sets. | Select gear, such as cables, pulleys, and winches, according to load weights and sizes, facilities, and work schedules. | Signal or verbally direct workers engaged in hoisting and moving loads to ensure safety of workers and materials. | Test rigging to ensure safety and reliability. | Tilt, dip, and turn suspended loads to maneuver over, under, or around obstacles, using multi-point suspension techniques.</t>
+  </si>
+  <si>
+    <t>49-9097.00</t>
+  </si>
+  <si>
+    <t>Signal and Track Switch Repairers</t>
+  </si>
+  <si>
+    <t>Railroad Signal Maintainer | Signal Inspector | Signal Maintainer | Signal Maintenance Technician | Signal System Testing Maintainer | Signal Technician | Signal and Communications Maintainer | Signalman | Train Control Electronic Technician | Train Control Technician</t>
+  </si>
+  <si>
+    <t>Maintenance management software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Supervisory control and data acquisition SCADA software | Web browser software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Transportation | Mechanical | English Language | Public Safety and Security | Telecommunications | Engineering and Technology | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Arm-Hand Steadiness | Control Precision | Flexibility of Closure | Visualization | Manual Dexterity | Finger Dexterity | Visual Color Discrimination | Far Vision | Multilimb Coordination | Deductive Reasoning | Inductive Reasoning | Reaction Time | Near Vision | Perceptual Speed | Information Ordering | Oral Expression | Oral Comprehension | Depth Perception | Trunk Strength | Selective Attention | Speech Clarity | Speech Recognition | Auditory Attention | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Work With or Contribute to a Work Group or Team | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | In an Enclosed Vehicle or Operate Enclosed Equipment | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Exposed to Very Hot or Cold Temperatures | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Exposed to Contaminants | Importance of Being Exact or Accurate | Frequency of Decision Making | Time Pressure | Impact of Decisions on Co-workers or Company Results | Spend Time Standing | Exposed to Hazardous Equipment | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Avionics Technicians | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical Power-Line Installers and Repairers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Electricians | Lighting Technicians | Locomotive Engineers | Mobile Heavy Equipment Mechanics, Except Engines | Power Distributors and Dispatchers | Radio, Cellular, and Tower Equipment Installers and Repairers | Rail Car Repairers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Telecommunications Equipment Installers and Repairers, Except Line Installers | Telecommunications Line Installers and Repairers</t>
+  </si>
+  <si>
+    <t>Install, inspect, test, maintain, or repair electric gate crossings, signals, signal equipment, track switches, section lines, or intercommunications systems within a railroad system.</t>
+  </si>
+  <si>
+    <t>Clean lenses of lamps with cloths and solvents. | Drive motor vehicles to job sites. | Inspect and test operation, mechanical parts, and circuitry of gate crossings, signals, and signal equipment such as interlocks and hotbox detectors. | Inspect electrical units of railroad grade crossing gates and repair loose bolts and defective electrical connections and parts. | Inspect switch-controlling mechanisms on trolley wires and in track beds, using hand tools and test equipment. | Inspect, maintain, and replace batteries as needed. | Install, inspect, maintain, and repair various railroad service equipment on the road or in the shop, including railroad signal systems. | Lubricate moving parts on gate-crossing mechanisms and swinging signals. | Record and report information about mileage or track inspected, repairs performed, and equipment requiring replacement. | Replace defective wiring, broken lenses, or burned-out light bulbs. | Test and repair track circuits. | Tighten loose bolts, using wrenches, and test circuits and connections by opening and closing gates.</t>
+  </si>
+  <si>
+    <t>49-9098.00</t>
+  </si>
+  <si>
+    <t>Helpers--Installation, Maintenance, and Repair Workers</t>
+  </si>
+  <si>
+    <t>HVAC Helper (Heating, Ventilation, Air Conditioning Helper) | HVAC Installation Helper (Heating, Ventilation, Air Conditioning Installation Helper) | Maintenance Aide | Maintenance Helper | Mechanic Helper | Mechanic Repair Helper | Mechanic's Assistant | Technician's Helper</t>
+  </si>
+  <si>
+    <t>Atlas Construction Business Forms | Building automation software | Data logging software | Facility energy management software | HVAC tools software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Customer and Personal Service | Public Safety and Security | English Language | Engineering and Technology | Mathematics | Design | Production and Processing | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Arm-Hand Steadiness | Near Vision | Control Precision | Multilimb Coordination | Finger Dexterity | Extent Flexibility | Trunk Strength | Static Strength | Information Ordering | Deductive Reasoning | Oral Comprehension | Selective Attention | Visualization | Flexibility of Closure | Problem Sensitivity | Oral Expression | Speech Recognition | Stamina</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Not Environmentally Controlled | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Contact With Others | Spend Time Standing | Frequency of Decision Making | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | E-Mail | Exposed to Minor Burns, Cuts, Bites, or Stings | Consequence of Error | Physical Proximity | Work Outcomes and Results of Other Workers</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Helpers--Brickmasons, Blockmasons, Stonemasons, and Tile and Marble Setters | Helpers--Carpenters | Helpers--Electricians | Helpers--Extraction Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Helpers--Production Workers | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Plumbers, Pipefitters, and Steamfitters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Help installation, maintenance, and repair workers in maintenance, parts replacement, and repair of vehicles, industrial machinery, and electrical and electronic equipment. Perform duties such as furnishing tools, materials, and supplies to other workers; cleaning work area, machines, and tools; and holding materials or tools for other workers.</t>
+  </si>
+  <si>
+    <t>Adjust, connect, or disconnect wiring, piping, tubing, and other parts, using hand or power tools. | Adjust, maintain, and repair tools, equipment, and machines, and assist more skilled workers with similar tasks. | Apply protective materials to equipment, components, and parts to prevent defects and corrosion. | Assemble and maintain physical structures, using hand or power tools. | Clean or lubricate vehicles, machinery, equipment, instruments, tools, work areas, and other objects, using hand tools, power tools, and cleaning equipment. | Design, weld, and fabricate parts, using blueprints or other mechanical plans. | Diagnose electrical problems and install and rewire electrical components. | Disassemble broken or defective equipment to facilitate repair and reassemble equipment when repairs are complete. | Examine and test machinery, equipment, components, and parts for defects to ensure proper functioning. | Hold or supply tools, parts, equipment, and supplies for other workers. | Install or replace machinery, equipment, and new or replacement parts and instruments, using hand or power tools. | Order new parts to maintain inventory. | Position vehicles, machinery, equipment, physical structures, and other objects for assembly or installation, using hand tools, power tools, and moving equipment. | Prepare work stations for use by mechanics and repairers. | Tend and observe equipment and machinery to verify efficient and safe operation. | Transfer tools, parts, equipment, and supplies to and from work stations and other areas.</t>
+  </si>
+  <si>
+    <t>49-9099.00</t>
+  </si>
+  <si>
+    <t>Installation, Maintenance, and Repair Workers, All Other</t>
+  </si>
+  <si>
+    <t>Equipment Repairer | Facilities Technician | Field Service Technician | Installation Technician | Maintenance Mechanic | Maintenance Technician | Repair Technician | Service Technician | Systems Technician | Installation and Repair Worker</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Mechanical | Building and Construction | Computers and Electronics | English Language | Engineering and Technology | Customer and Personal Service | Mathematics | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Health and Safety of Other Workers | Physical Proximity | Telephone Conversations | Deal With External Customers or the Public in General | Freedom to Make Decisions | Contact With Others | Time Pressure</t>
+  </si>
+  <si>
+    <t>Maintenance and Repair Workers, General | Industrial Machinery Mechanics | Maintenance Workers, Machinery | Millwrights | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Security and Fire Alarm Systems Installers | Home Appliance Repairers | Coin, Vending, and Amusement Machine Servicers and Repairers | Locksmiths and Safe Repairers | Mechanical Door Repairers | Manufactured Building and Mobile Home Installers | Wind Turbine Service Technicians | Geothermal Technicians | Riggers | Helpers--Installation, Maintenance, and Repair Workers | First-Line Supervisors of Mechanics, Installers, and Repairers | Electricians | Plumbers, Pipefitters, and Steamfitters | Facilities Managers</t>
+  </si>
+  <si>
+    <t>All installation, maintenance, and repair workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Install, maintain, and repair equipment in roles not classified separately. | Diagnose equipment problems using diagnostic tools, manuals, and experience. | Disassemble, repair, replace, and reassemble defective components. | Install new equipment and verify correct operation after commissioning. | Perform scheduled preventive maintenance, inspections, and adjustments. | Test systems after service to verify performance and safety. | Read blueprints, wiring diagrams, and technical specifications. | Order and maintain inventories of parts, tools, and consumables. | Record service performed, parts used, and time expended. | Advise customers or users on operation, care, and maintenance schedules. | Follow lockout procedures, electrical safety, and hazard controls. | Fabricate or modify parts and fittings when standard components are unavailable. | Respond to emergency service calls and prioritize repairs by urgency. | Coordinate work with vendors, contractors, and other trades.</t>
+  </si>
+  <si>
+    <t>49-9099.01</t>
+  </si>
+  <si>
+    <t>Geothermal Technicians</t>
+  </si>
+  <si>
+    <t>Geothermal Service Technician | I C and E Technician (Instrumentation, Control, and Electrical Technician) | I and C Technician (Instrument and Controls Technician) | I and E Technician (Instrumentation and Electrical Technician) | Operations Technician | Operations and Maintenance Technician (O and M Technician) | Operator Technician | Plant Electrical Technician | Plant Mechanic | Plant Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | ClimateMaster GeoDesigner | Distributed control system DCS | Email software | Geographic information system GIS systems | Geothermal Properties Measurement Tool | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | SAP software | Thermal Dynamics Ground Loop Design GLD | WaterFurnace International Ground Loop Design PREMIER</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Critical Thinking | Active Learning | Speaking | Writing | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | English Language | Physics | Education and Training | Public Safety and Security | Chemistry | Telecommunications | Design | Mathematics | Production and Processing | Administration and Management | Computers and Electronics | Administrative | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Deductive Reasoning | Perceptual Speed | Arm-Hand Steadiness | Information Ordering | Flexibility of Closure | Visualization | Selective Attention | Control Precision | Speech Recognition | Visual Color Discrimination | Extent Flexibility | Multilimb Coordination | Inductive Reasoning | Written Expression | Oral Expression | Oral Comprehension | Written Comprehension | Speech Clarity | Far Vision | Trunk Strength | Reaction Time | Finger Dexterity | Manual Dexterity | Time Sharing | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Telephone Conversations | Exposed to Hazardous Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Outdoors, Exposed to All Weather Conditions | E-Mail | Exposed to Contaminants | Health and Safety of Other Workers | Frequency of Decision Making | Contact With Others | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Consequence of Error | Indoors, Environmentally Controlled | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | Importance of Repeating Same Tasks | Exposed to Hazardous Equipment | Importance of Being Exact or Accurate | Time Pressure | Exposed to Extremely Bright or Inadequate Lighting Conditions</t>
+  </si>
+  <si>
+    <t>Biomass Plant Technicians | Biomass Power Plant Managers | Control and Valve Installers and Repairers, Except Mechanical Door | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electrical and Electronics Repairers, Powerhouse, Substation, and Relay | Gas Compressor and Gas Pumping Station Operators | Gas Plant Operators | Geothermal Production Managers | Heating, Air Conditioning, and Refrigeration Mechanics and Installers | Hydroelectric Plant Technicians | Hydroelectric Production Managers | Mechanical Engineers | Power Distributors and Dispatchers | Power Plant Operators | Solar Photovoltaic Installers | Solar Thermal Installers and Technicians | Stationary Engineers and Boiler Operators | Water and Wastewater Treatment Plant and System Operators | Wellhead Pumpers | Wind Turbine Service Technicians</t>
+  </si>
+  <si>
+    <t>Perform technical activities at power plants or individual installations necessary for the generation of power from geothermal energy sources. Monitor and control operating activities at geothermal power generation facilities and perform maintenance and repairs as necessary. Install, test, and maintain residential and commercial geothermal heat pumps.</t>
+  </si>
+  <si>
+    <t>Adjust power production systems to meet load and distribution demands. | Apply coatings or operate systems to mitigate corrosion of geothermal plant equipment or structures. | Backfill piping trenches to protect pipes from damage. | Calculate heat loss and heat gain factors for residential properties to determine heating and cooling required by installed geothermal systems. | Collect and record data associated with operating geothermal power plants or well fields. | Design and lay out geothermal heat systems according to property characteristics, heating and cooling requirements, piping and equipment requirements, applicable regulations, or other factors. | Determine the type of geothermal loop system most suitable to a specific property and its heating and cooling needs. | Determine whether emergency or auxiliary systems will be needed to keep properties heated or cooled in extreme weather conditions. | Dig trenches for system piping to appropriate depths and lay piping in trenches. | Identify and correct malfunctions of geothermal plant equipment, electrical systems, instrumentation, or controls. | Identify equipment options, such as compressors, and make appropriate selections. | Install and maintain geothermal plant electrical protection equipment. | Install and maintain geothermal system instrumentation or controls. | Install, maintain, or repair ground or water source-coupled heat pumps to heat and cool residential or commercial building air or water. | Integrate hot water heater systems with geothermal heat exchange systems. | Maintain electrical switchgear, process controls, transmitters, gauges, and control equipment in accordance with geothermal plant procedures. | Maintain, calibrate, or repair plant instrumentation, control, and electronic devices in geothermal plants. | Monitor and adjust operations of geothermal power plant equipment or systems. | Operate equipment, such as excavators, backhoes, rock hammers, trench compactors, pavement saws, grout mixers or pumps, geothermal loop reels, and coil tubing units (CTU). | Perform pre- and post-installation pressure, flow, and related tests of vertical and horizontal geothermal loop piping. | Prepare and maintain logs, reports, or other documentation of work performed. | Prepare newly installed geothermal heat systems for operation by flushing, purging, or other actions. | Test water sources for factors, such as flow volume and contaminant presence. | Weld piping, such as high density polyethylene (HDPE) piping, using techniques such as butt, socket, side-wall, and electro-fusion welding.</t>
+  </si>
+  <si>
+    <t>51-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Production and Operating Workers</t>
+  </si>
+  <si>
+    <t>Assembly Supervisor | Line Supervisor | Manufacturing Supervisor | Molding Supervisor | Plant Supervisor | Production Manager | Production Supervisor | Quality Assurance Supervisor (QA Supervisor)</t>
+  </si>
+  <si>
+    <t>Apple Safari | Apple iWork Pages | Aptean Made2Manage | Autodesk AutoCAD | Bowen &amp; Groves M1 ERP | Capterra Enterprise Resource Planning | Database software | Delphi Technology | Email software | Encompix ERP | Epicor Vantage ERP | Epicor Vista ERP | Exact MAX | Extensible markup language XML | GHG Clockwise | Giraffe Production Systems Giraffe Schedule System | Google Chrome | HCSS HeavyJob | IBM Notes | Intacct ERP | Integrated materials management systems | Kronos Workforce Timekeeper | Materials management software | Microsoft Access | Microsoft Axapta | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Total Quality Control Management | Microsoft Word | Minitab | Mozilla Firefox | NetSuite NetERP | Operational databases | Oracle JD Edwards EnterpriseOne | QA Software QMS Materials Management | Resource planning software | Retain Resource Planning | SAP Business One | SAP software | SYSPRO business software | Supervisory control and data acquisition SCADA software | Technology Group International Enterprise 21 ERP | Timekeeping software | Total quality management TQM software | Work Technology WorkTech Time</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Reading Comprehension | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Production and Processing | Administration and Management | Personnel and Human Resources | English Language | Computers and Electronics | Mathematics | Administrative | Mechanical | Education and Training | Engineering and Technology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Written Comprehension | Deductive Reasoning | Speech Recognition | Speech Clarity | Written Expression | Inductive Reasoning | Information Ordering | Category Flexibility | Near Vision | Visualization | Perceptual Speed | Originality | Fluency of Ideas | Selective Attention | Flexibility of Closure | Mathematical Reasoning | Far Vision | Manual Dexterity | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Time Pressure | Frequency of Decision Making | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | E-Mail | Freedom to Make Decisions | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Not Environmentally Controlled | Telephone Conversations | Spend Time Standing | Pace Determined by Speed of Equipment | Conflict Situations | Exposed to Contaminants | Exposed to Very Hot or Cold Temperatures | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Security Workers | General and Operations Managers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Industrial Production Managers | Production, Planning, and Expediting Clerks | Recycling Coordinators | Team Assemblers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate the activities of production and operating workers, such as inspectors, precision workers, machine setters and operators, assemblers, fabricators, and plant and system operators. Excludes team or work leaders.</t>
+  </si>
+  <si>
+    <t>Calculate labor and equipment requirements and production specifications, using standard formulas. | Conduct employee training in equipment operations or work and safety procedures, or assign employee training to experienced workers. | Confer with management or subordinates to resolve worker problems, complaints, or grievances. | Confer with other supervisors to coordinate operations and activities within or between departments. | Determine standards, budgets, production goals, and rates, based on company policies, equipment and labor availability, and workloads. | Direct and coordinate the activities of employees engaged in the production or processing of goods, such as inspectors, machine setters, or fabricators. | Enforce safety and sanitation regulations. | Evaluate employee performance. | Inspect materials, products, or equipment to detect defects or malfunctions. | Interpret specifications, blueprints, job orders, and company policies and procedures for workers. | Keep records of employees' attendance and hours worked. | Maintain operations data, such as time, production, and cost records, and prepare management reports of production results. | Observe work and monitor gauges, dials, and other indicators to ensure that operators conform to production or processing standards. | Plan and develop new products and production processes. | Plan and establish work schedules, assignments, and production sequences to meet production goals. | Read and analyze charts, work orders, production schedules, and other records and reports to determine production requirements and to evaluate current production estimates and outputs. | Recommend or execute personnel actions, such as hirings, evaluations, or promotions. | Recommend or implement measures to motivate employees and to improve production methods, equipment performance, product quality, or efficiency. | Requisition materials, supplies, equipment parts, or repair services. | Set up and adjust machines and equipment.</t>
+  </si>
+  <si>
+    <t>51-2011.00</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers</t>
+  </si>
+  <si>
+    <t>A&amp;P Technician (Airframe and Powerplant Technician) | Aircraft Line Assembler | Assembler | Assembly Riveter | Helicopter Technician | Sheet Metal Assembler and Riveter (SMAR) | Sheet Metal Mechanic | Structures Mechanic | Structures Technician</t>
+  </si>
+  <si>
+    <t>Electrical power management system software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Critical Thinking | Monitoring | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mathematics | Education and Training | Mechanical | English Language | Production and Processing | Design | Computers and Electronics | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Near Vision | Finger Dexterity | Manual Dexterity | Visualization | Information Ordering | Speech Recognition | Extent Flexibility | Control Precision | Arm-Hand Steadiness | Deductive Reasoning | Written Comprehension | Oral Comprehension | Inductive Reasoning | Oral Expression | Speech Clarity | Auditory Attention | Multilimb Coordination | Selective Attention | Perceptual Speed | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Importance of Being Exact or Accurate | Exposed to Hazardous Conditions | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Spend Time Standing | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Time Pressure</t>
+  </si>
+  <si>
+    <t>Aircraft Mechanics and Service Technicians | Avionics Technicians | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electro-Mechanical and Mechatronics Technologists and Technicians | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Layout Workers, Metal and Plastic | Machinists | Maintenance Workers, Machinery | Maintenance and Repair Workers, General | Millwrights | Model Makers, Metal and Plastic | Sheet Metal Workers | Structural Metal Fabricators and Fitters | Timing Device Assemblers and Adjusters | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Assemble, fit, fasten, and install parts of airplanes, space vehicles, or missiles, such as tails, wings, fuselage, bulkheads, stabilizers, landing gear, rigging and control equipment, or heating and ventilating systems.</t>
+  </si>
+  <si>
+    <t>Adjust, repair, rework, or replace parts or assemblies to ensure proper operation. | Align, fit, assemble, connect, or install system components, using jigs, fixtures, measuring instruments, hand tools, or power tools. | Assemble parts, fittings, or subassemblies on aircraft, using layout tools, hand tools, power tools, or fasteners, such as bolts, screws, rivets, or clamps. | Assemble prefabricated parts to form subassemblies. | Assemble prototypes or integrated-technology demonstrators of new or emerging environmental technologies for aircraft. | Attach brackets, hinges, or clips to secure or support components or subassemblies, using bolts, screws, rivets, chemical bonding, or welding. | Capture or segregate waste material, such as aluminum swarf, machine cutting fluid, or solvents, for recycling or environmentally responsible disposal. | Clean aircraft structures, parts, or components, using aqueous, semi-aqueous, aliphatic hydrocarbon, or organic solvent cleaning products or techniques to reduce carbon or other harmful emissions. | Clean, oil, or coat system components, as necessary, before assembly or attachment. | Cut cables and tubing, using master templates, measuring instruments, and cable cutters or saws. | Cut, trim, file, bend, or smooth parts to ensure proper fit and clearance. | Fabricate parts needed for assembly or installation, using shop machinery or equipment. | Fit and fasten sheet metal coverings to surface areas or other sections of aircraft prior to welding or riveting. | Inspect or test installed units, parts, systems, or assemblies for fit, alignment, performance, defects, or compliance with standards, using measuring instruments or test equipment. | Install accessories in swaging machines, using hand tools. | Install mechanical linkages and actuators, using tensiometers to verify tension of cables. | Join structural assemblies, such as wings, tails, or fuselage. | Layout and mark reference points and locations for installation of parts or components, using jigs, templates, or measuring and marking instruments. | Manually install structural assemblies or signal crane operators to position assemblies for joining. | Mark identifying information on tubing or cable assemblies, using etching devices, labels, rubber stamps, or other methods. | Place and connect control cables to electronically controlled units, using hand tools, ring locks, cotter keys, threaded connectors, turnbuckles, or related devices. | Position and align subassemblies in jigs or fixtures, using measuring instruments and following blueprint lines and index points. | Read blueprints, illustrations, or specifications to determine layouts, sequences of operations, or identities or relationships of parts. | Set up or operate machines or systems to crimp, cut, bend, form, swage, flare, bead, burr, or straighten tubing, according to specifications. | Set, align, adjust, or synchronize aircraft armament or rigging or control system components to established tolerances or requirements, using sighting devices and hand tools. | Verify dimensions of cable assemblies or positions of fittings, using measuring instruments. | Weld tubing and fittings or solder cable ends, using tack welders, induction brazing chambers, or other equipment.</t>
+  </si>
+  <si>
+    <t>51-2021.00</t>
+  </si>
+  <si>
+    <t>Coil Winders, Tapers, and Finishers</t>
+  </si>
+  <si>
+    <t>Armature Winder | Auto-Winder | Coil Finisher | Coil Winder | Hand Winder | Motor Winder | Winder | Winder Operator</t>
+  </si>
+  <si>
+    <t>Blueprint display software | Electronic Systems of Wisconsin Motor Test System software | Machine Control Specialists CoilPro</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening</t>
+  </si>
+  <si>
+    <t>Education and Training | English Language | Mathematics | Administration and Management | Production and Processing | Mechanical | Design | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Control Precision | Near Vision | Finger Dexterity | Selective Attention | Problem Sensitivity | Speech Clarity | Speech Recognition | Deductive Reasoning | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Contaminants | Time Pressure | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Consequence of Error | Exposed to Minor Burns, Cuts, Bites, or Stings | Determine Tasks, Priorities and Goals | Contact With Others | Importance of Repeating Same Tasks | Indoors, Environmentally Controlled | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Engine and Other Machine Assemblers | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Timing Device Assemblers and Adjusters | Tool Grinders, Filers, and Sharpeners | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Wind wire coils used in electrical components, such as resistors and transformers, and in electrical equipment and instruments, such as field cores, bobbins, armature cores, electrical motors, generators, and control equipment.</t>
+  </si>
+  <si>
+    <t>Apply solutions or paints to wired electrical components, using hand tools, and bake components. | Attach, alter, and trim materials such as wire, insulation, and coils, using hand tools. | Cut, strip, and bend wire leads at ends of coils, using pliers and wire scrapers. | Disassemble and assemble motors, and repair and maintain electrical components and machinery parts, using hand tools. | Examine and test wired electrical components such as motors, armatures, and stators, using measuring devices, and record test results. | Line slots with sheet insulation, and insert coils into slots. | Operate or tend wire-coiling machines to wind wire coils used in electrical components such as resistors and transformers, and in electrical equipment and instruments such as bobbins and generators. | Record production and operational data on specified forms. | Review work orders and specifications to determine materials needed and types of parts to be processed. | Select and load materials such as workpieces, objects, and machine parts onto equipment used in coiling processes. | Stop machines to remove completed components, using hand tools.</t>
+  </si>
+  <si>
+    <t>51-2022.00</t>
+  </si>
+  <si>
+    <t>Electrical and Electronic Equipment Assemblers</t>
+  </si>
+  <si>
+    <t>Assembler | Assembly Worker | Electrical Assembler | Electronic Assembler | Electronics Assembler | Factory Assembler | Manufacturing Assembler | Transformer Assembler</t>
+  </si>
+  <si>
+    <t>Calibration software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | National Instruments LabVIEW | Production control software | Rasmussen Software Anzio | SAP software | Sage 100 ERP | Terminal emulation software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Computers and Electronics | Mechanical | English Language | Mathematics | Engineering and Technology | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Finger Dexterity | Oral Comprehension | Manual Dexterity | Arm-Hand Steadiness | Information Ordering | Visualization | Inductive Reasoning | Oral Expression | Written Comprehension | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Visual Color Discrimination | Multilimb Coordination | Control Precision</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Coil Winders, Tapers, and Finishers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Machinists | Mechanical Engineers | Model Makers, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Team Assemblers | Timing Device Assemblers and Adjusters | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Assemble or modify electrical or electronic equipment, such as computers, test equipment telemetering systems, electric motors, and batteries.</t>
+  </si>
+  <si>
+    <t>Adjust, repair, or replace electrical or electronic components to correct defects and to ensure conformance to specifications. | Assemble electrical or electronic systems or support structures and install components, units, subassemblies, wiring, or assembly casings, using rivets, bolts, soldering or micro-welding equipment. | Clean parts, using cleaning solutions, air hoses, and cloths. | Complete, review, or maintain production, time, or component waste reports. | Confer with supervisors or engineers to plan or review work activities or to resolve production problems. | Distribute materials, supplies, or subassemblies to work areas. | Drill or tap holes in specified equipment locations to mount control units or to provide openings for elements, wiring, or instruments. | Explain assembly procedures or techniques to other workers. | Fabricate or form parts, coils, or structures according to specifications, using drills, calipers, cutters, or saws. | Inspect or test wiring installations, assemblies, or circuits for resistance factors or for operation, and record results. | Instruct customers in the installation, repair, or maintenance of products. | Mark and tag components so that stock inventory can be tracked and identified. | Measure and adjust voltages to specified values to determine operational accuracy of instruments. | Pack finished assemblies for shipment, and transport them to storage areas, using hoists or handtrucks. | Position, align, or adjust workpieces or electrical parts to facilitate wiring or assembly. | Read and interpret schematic drawings, diagrams, blueprints, specifications, work orders, or reports to determine materials requirements or assembly instructions.</t>
+  </si>
+  <si>
+    <t>51-2023.00</t>
+  </si>
+  <si>
+    <t>Electromechanical Equipment Assemblers</t>
+  </si>
+  <si>
+    <t>Assembler | Electrical Assembler | Electromechanical Assembler | Electromechanical Equipment Assembler | Electronic Assembler | Electronic Technician | Electronics Assembler | Mechanical Assembler | Production Associate | Wiring Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Blueprint display software | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software | Timekeeping software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Near Vision | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Problem Sensitivity | Information Ordering | Control Precision | Visualization | Deductive Reasoning | Speech Clarity | Speech Recognition | Visual Color Discrimination | Far Vision | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Oral Expression | Written Comprehension | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Contact With Others | Health and Safety of Other Workers | Time Pressure | Freedom to Make Decisions | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Computer Numerically Controlled Tool Operators | Computer Numerically Controlled Tool Programmers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Installers and Repairers, Transportation Equipment | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electronics Engineers, Except Computer | Engine and Other Machine Assemblers | Industrial Machinery Mechanics | Machinists | Millwrights | Model Makers, Metal and Plastic | Robotics Technicians | Team Assemblers | Timing Device Assemblers and Adjusters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Assemble or modify electromechanical equipment or devices, such as servomechanisms, gyros, dynamometers, magnetic drums, tape drives, brakes, control linkage, actuators, and appliances.</t>
+  </si>
+  <si>
+    <t>Assemble parts or units, and position, align, and fasten units to assemblies, subassemblies, or frames, using hand tools and power tools. | Attach name plates and mark identifying information on parts. | Clean and lubricate parts and subassemblies, using grease paddles or oilcans. | Connect cables, tubes, and wiring, according to specifications. | Disassemble units to replace parts or to crate them for shipping. | Drill, tap, ream, countersink, and spot-face bolt holes in parts, using drill presses and portable power drills. | File, lap, and buff parts to fit, using hand and power tools. | Inspect, test, and adjust completed units to ensure that units meet specifications, tolerances, and customer order requirements. | Measure parts to determine tolerances, using precision measuring instruments such as micrometers, calipers, and verniers. | Operate or tend automated assembling equipment, such as robotics and fixed automation equipment. | Operate small cranes to transport or position large parts. | Pack or fold insulation between panels. | Position, align, and adjust parts for proper fit and assembly. | Read blueprints and specifications to determine component parts and assembly sequences of electromechanical units.</t>
+  </si>
+  <si>
+    <t>51-2031.00</t>
+  </si>
+  <si>
+    <t>Engine and Other Machine Assemblers</t>
+  </si>
+  <si>
+    <t>Assembler | Assembly Line Worker | Cell Technician | Engine Assembler | Engine Builder | Field Service Technician | Fitter | Large Engine Assembler | Machine Assembler | Mechanical Assembler</t>
+  </si>
+  <si>
+    <t>Computer aided design and drafting CADD software | Dassault Systemes SolidWorks | Microsoft Excel | Microsoft Office software | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Monitoring | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Manual Dexterity | Finger Dexterity | Near Vision | Visualization | Extent Flexibility | Static Strength | Multilimb Coordination | Control Precision | Information Ordering | Problem Sensitivity | Written Comprehension | Oral Comprehension | Selective Attention | Perceptual Speed | Flexibility of Closure | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Speech Clarity | Speech Recognition | Trunk Strength</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Work With or Contribute to a Work Group or Team | Contact With Others | Exposed to Contaminants | Health and Safety of Other Workers | Exposed to Hazardous Equipment | Frequency of Decision Making | Physical Proximity | Spend Time Bending or Twisting Your Body | Indoors, Not Environmentally Controlled | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Bus and Truck Mechanics and Diesel Engine Specialists | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Layout Workers, Metal and Plastic | Machinists | Maintenance Workers, Machinery | Mechanical Engineers | Millwrights | Mobile Heavy Equipment Mechanics, Except Engines | Model Makers, Metal and Plastic | Rail Car Repairers | Structural Metal Fabricators and Fitters | Timing Device Assemblers and Adjusters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Construct, assemble, or rebuild machines, such as engines, turbines, and similar equipment used in such industries as construction, extraction, textiles, and paper manufacturing.</t>
+  </si>
+  <si>
+    <t>Assemble systems of gears by aligning and meshing gears in gearboxes. | Fasten or install piping, fixtures, or wiring and electrical components to form assemblies or subassemblies, using hand tools, rivet guns, or welding equipment. | Inspect, operate, and test completed products to verify functioning, machine capabilities, or conformance to customer specifications. | Lay out and drill, ream, tap, or cut parts for assembly. | Maintain and lubricate parts or components. | Position or align components for assembly, manually or using hoists. | Read and interpret assembly blueprints or specifications manuals, and plan assembly or building operations. | Remove rough spots and smooth surfaces to fit, trim, or clean parts, using hand tools or power tools. | Rework, repair, or replace damaged parts or assemblies. | Set and verify parts clearances. | Set up and operate metalworking machines, such as milling or grinding machines, to shape or fabricate parts. | Verify conformance of parts to stock lists or blueprints, using measuring instruments such as calipers, gauges, or micrometers.</t>
+  </si>
+  <si>
+    <t>51-2041.00</t>
+  </si>
+  <si>
+    <t>Structural Metal Fabricators and Fitters</t>
+  </si>
+  <si>
+    <t>Fabricator | Fitter | Layout Man | Metal Fabricator | Mill Beam Fitter | Ship Fitter | Small Parts Fabricator | Steel Fabricator | Structural Planner | Structural Steel Fitter</t>
+  </si>
+  <si>
+    <t>Computer aided design and drafting CADD software | Dassault Systemes CATIA | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Tekla software | Three-dimensional modeling software</t>
+  </si>
+  <si>
+    <t>Active Listening | Reading Comprehension | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Mathematics | Production and Processing | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Near Vision | Static Strength | Multilimb Coordination | Control Precision | Manual Dexterity | Visualization | Selective Attention | Category Flexibility | Information Ordering | Deductive Reasoning | Problem Sensitivity | Oral Expression | Trunk Strength | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Time Pressure | Spend Time Standing | Contact With Others | Work With or Contribute to a Work Group or Team | Exposed to Hazardous Equipment | Determine Tasks, Priorities and Goals | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings | Freedom to Make Decisions | Health and Safety of Other Workers | Spend Time Making Repetitive Motions</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Boilermakers | Carpenters | Electrical and Electronic Equipment Assemblers | Engine and Other Machine Assemblers | Grinding and Polishing Workers, Hand | Layout Workers, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Millwrights | Model Makers, Metal and Plastic | Molders, Shapers, and Casters, Except Metal and Plastic | Patternmakers, Metal and Plastic | Reinforcing Iron and Rebar Workers | Sheet Metal Workers | Structural Iron and Steel Workers | Tool and Die Makers | Welders, Cutters, Solderers, and Brazers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Fabricate, position, align, and fit parts of structural metal products.</t>
+  </si>
+  <si>
+    <t>Align and fit parts according to specifications, using jacks, turnbuckles, wedges, drift pins, pry bars, and hammers. | Design and construct templates and fixtures, using hand tools. | Direct welders to build up low spots or short pieces with weld. | Erect ladders and scaffolding to fit together large assemblies. | Hammer, chip, and grind workpieces to cut, bend, and straighten metal. | Heat-treat parts, using acetylene torches. | Install boilers, containers, and other structures. | Lay out and examine metal stock or workpieces to be processed to ensure that specifications are met. | Lift or move materials and finished products, using large cranes. | Locate and mark workpiece bending and cutting lines, allowing for stock thickness, machine and welding shrinkage, and other component specifications. | Mark reference points onto floors or face blocks and transpose them to workpieces, using measuring devices, squares, chalk, and soapstone. | Move parts into position, manually or with hoists or cranes. | Position or tighten braces, jacks, clamps, ropes, or bolt straps, or bolt parts in position for welding or riveting. | Position, align, fit, and weld parts to form complete units or subunits, following blueprints and layout specifications, and using jigs, welding torches, and hand tools. | Preheat workpieces to make them malleable, using hand torches or furnaces. | Remove high spots and cut bevels, using hand files, portable grinders, and cutting torches. | Set up and operate fabricating machines, such as brakes, rolls, shears, flame cutters, grinders, and drill presses, to bend, cut, form, punch, drill, or otherwise form and assemble metal components. | Set up face blocks, jigs, and fixtures. | Smooth workpiece edges and fix taps, tubes, and valves. | Straighten warped or bent parts, using sledges, hand torches, straightening presses, or bulldozers. | Study engineering drawings and blueprints to determine materials requirements and task sequences. | Tack-weld fitted parts together. | Verify conformance of workpieces to specifications, using squares, rulers, and measuring tapes.</t>
+  </si>
+  <si>
+    <t>51-2051.00</t>
+  </si>
+  <si>
+    <t>Fiberglass Laminators and Fabricators</t>
+  </si>
+  <si>
+    <t>Boat Builder | Boat Carpenter | Chopper Gun Operator | Fiberglass Laminator | Fiberglass Technician | Fiberglasser | Gel-Coater | Lamination Technician | Laminator | Roller</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Administration and Management | Production and Processing | Education and Training | Chemistry | English Language | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Arm-Hand Steadiness | Multilimb Coordination | Trunk Strength | Near Vision | Oral Comprehension | Information Ordering | Visualization | Extent Flexibility | Visual Color Discrimination | Static Strength | Control Precision | Manual Dexterity | Selective Attention | Flexibility of Closure | Perceptual Speed | Category Flexibility | Inductive Reasoning | Deductive Reasoning | Oral Expression | Written Comprehension | Finger Dexterity | Speech Clarity | Speech Recognition | Stamina</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Wear Specialized Protective or Safety Equipment such as Breathing Apparatus, Safety Harness, Full Protection Suits, or Radiation Protection | Exposed to Contaminants | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Physical Proximity | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Contact With Others | Spend Time Bending or Twisting Your Body | Work Outcomes and Results of Other Workers | Health and Safety of Other Workers | Exposed to Hazardous Conditions | Importance of Being Exact or Accurate | Spend Time Kneeling, Crouching, Stooping, or Crawling | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Coil Winders, Tapers, and Finishers | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Foundry Mold and Coremakers | Furniture Finishers | Grinding and Polishing Workers, Hand | Insulation Workers, Floor, Ceiling, and Wall | Insulation Workers, Mechanical | Machine Feeders and Offbearers | Molders, Shapers, and Casters, Except Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Painting, Coating, and Decorating Workers | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Refractory Materials Repairers, Except Brickmasons | Structural Metal Fabricators and Fitters | Tire Builders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Laminate layers of fiberglass on molds to form boat decks and hulls, bodies for golf carts, automobiles, or other products.</t>
+  </si>
+  <si>
+    <t>Apply lacquers and waxes to mold surfaces to facilitate assembly and removal of laminated parts. | Apply layers of plastic resin to mold surfaces prior to placement of fiberglass mats, repeating layers until products have the desired thicknesses and plastics have jelled. | Bond wood reinforcing strips to decks and cabin structures of watercraft, using resin-saturated fiberglass. | Check all dies, templates, and cutout patterns to be used in the manufacturing process to ensure that they conform to dimensional data, photographs, blueprints, samples, or customer specifications. | Check completed products for conformance to specifications and for defects by measuring with rulers or micrometers, by checking them visually, or by tapping them to detect bubbles or dead spots. | Cure materials by letting them set at room temperature, placing them under heat lamps, or baking them in ovens. | Inspect, clean, and assemble molds before beginning work. | Mask off mold areas not to be laminated, using cellophane, wax paper, masking tape, or special sprays containing mold-release substances. | Mix catalysts into resins, and saturate cloth and mats with mixtures, using brushes. | Pat or press layers of saturated mat or cloth into place on molds, using brushes or hands, and smooth out wrinkles and air bubbles with hands or squeegees. | Release air bubbles and smooth seams, using rollers. | Repair or modify damaged or defective glass-fiber parts, checking thicknesses, densities, and contours to ensure a close fit after repair. | Select precut fiberglass mats, cloth, and wood-bracing materials as required by projects being assembled. | Spray chopped fiberglass, resins, and catalysts onto prepared molds or dies using pneumatic spray guns with chopper attachments. | Trim cured materials by sawing them with diamond-impregnated cutoff wheels. | Trim excess materials from molds, using hand shears or trimming knives.</t>
+  </si>
+  <si>
+    <t>51-2061.00</t>
+  </si>
+  <si>
+    <t>Timing Device Assemblers and Adjusters</t>
+  </si>
+  <si>
+    <t>Calibration Specialist | Calibrator | Clockmaker | Horologist | Time Stamp Assembler | Watch Technician | Watchmaker</t>
+  </si>
+  <si>
+    <t>At Your Service Software At Your Service Repair | Inventory control software | Maplesoft Maple | Microsoft Office software | Retail sales software | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Active Listening | Reading Comprehension | Speaking | Mathematics</t>
+  </si>
+  <si>
+    <t>Mechanical | Mathematics</t>
+  </si>
+  <si>
+    <t>Finger Dexterity | Arm-Hand Steadiness | Near Vision | Manual Dexterity | Problem Sensitivity | Control Precision | Visualization | Information Ordering | Oral Comprehension | Visual Color Discrimination | Category Flexibility | Deductive Reasoning | Oral Expression</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Contact With Others | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Frequency of Decision Making | Telephone Conversations | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Spend Time Sitting</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Calibration Technologists and Technicians | Coil Winders, Tapers, and Finishers | Control and Valve Installers and Repairers, Except Mechanical Door | Electric Motor, Power Tool, and Related Repairers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machinists | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Model Makers, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Structural Metal Fabricators and Fitters | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Watch and Clock Repairers</t>
+  </si>
+  <si>
+    <t>Perform precision assembling or adjusting, within narrow tolerances, of timing devices such as digital clocks or timing devices with electrical or electronic components.</t>
+  </si>
+  <si>
+    <t>Adjust sizes or positioning of timepiece parts to achieve specified fit or function, using calipers, fixtures, and loupes. | Assemble and install components of timepieces to complete mechanisms, using watchmakers' tools and loupes. | Bend inner coils of springs away from or toward collets, using tweezers, to locate centers of collets in centers of springs, and to correct errors resulting from faulty colleting of coils. | Bend parts, such as hairsprings, pallets, barrel covers, and bridges, to correct deficiencies in truing or endshake, using tweezers. | Change timing weights on balance wheels to correct deficient timing. | Clean and lubricate timepiece parts and assemblies, using solvents, buff sticks, and oil. | Disassemble timepieces such as watches, clocks, and chronometers so that repairs can be made. | Estimate spaces between collets and first inner coils to determine if spaces are within acceptable limits. | Examine and adjust hairspring assemblies to ensure horizontal and circular alignment of hairsprings, using calipers, loupes, and watchmakers' tools. | Examine components of timepieces such as watches, clocks, or chronometers for defects, using loupes or microscopes. | Mount hairsprings and balance wheel assemblies between jaws of truing calipers. | Observe operation of timepiece parts and subassemblies to determine accuracy of movement, and to diagnose causes of defects. | Replace specified parts to repair malfunctioning timepieces, using watchmakers' tools, loupes, and holding fixtures. | Review blueprints, sketches, or work orders to gather information about tasks to be completed. | Test operation and fit of timepiece parts and subassemblies, using electronic testing equipment, tweezers, watchmakers' tools, and loupes. | Tighten or replace loose jewels, using watchmakers' tools. | Turn wheels of calipers and examine springs, using loupes, to determine if center coils appear as perfect circles.</t>
+  </si>
+  <si>
+    <t>51-2092.00</t>
+  </si>
+  <si>
+    <t>Team Assemblers</t>
+  </si>
+  <si>
+    <t>Assembler | Assembly Associate | Assembly Line Machine Operator | Assembly Line Worker | Assembly Operator | Assembly Technician | Certified Composites Technician (CCT) | Manufacturing Associate | Production Line Worker</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | Public Safety and Security | English Language | Education and Training | Computers and Electronics | Design | Engineering and Technology | Mathematics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Near Vision | Information Ordering | Speech Clarity | Speech Recognition | Arm-Hand Steadiness | Deductive Reasoning | Problem Sensitivity | Oral Comprehension | Trunk Strength | Control Precision | Selective Attention | Visualization | Category Flexibility | Inductive Reasoning | Written Expression | Oral Expression | Written Comprehension | Far Vision</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Time Pressure | Work With or Contribute to a Work Group or Team | Contact With Others | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Physical Proximity | Frequency of Decision Making | Spend Time Standing | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants</t>
+  </si>
+  <si>
+    <t>Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronic Equipment Assemblers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | First-Line Supervisors of Production and Operating Workers | Industrial Engineering Technologists and Technicians | Industrial Engineers | Industrial Machinery Mechanics | Industrial Production Managers | Inspectors, Testers, Sorters, Samplers, and Weighers | Machinists | Manufacturing Engineers | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Millwrights | Robotics Technicians | Structural Metal Fabricators and Fitters | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Work as part of a team having responsibility for assembling an entire product or component of a product. Team assemblers can perform all tasks conducted by the team in the assembly process and rotate through all or most of them, rather than being assigned to a specific task on a permanent basis. May participate in making management decisions affecting the work. Includes team leaders who work as part of the team.</t>
+  </si>
+  <si>
+    <t>Complete production reports to communicate team production level to management. | Determine work assignments and procedures. | Maintain production equipment and machinery. | Operate machinery and heavy equipment, such as forklifts. | Package finished products and prepare them for shipment. | Perform quality checks on products and parts. | Provide assistance in the production of wiring assemblies. | Review work orders and blueprints to ensure work is performed according to specifications. | Rotate through all the tasks required in a particular production process. | Shovel, sweep, or otherwise clean work areas. | Supervise assemblers and train employees on job procedures.</t>
+  </si>
+  <si>
+    <t>51-2099.00</t>
+  </si>
+  <si>
+    <t>Assemblers and Fabricators, All Other</t>
+  </si>
+  <si>
+    <t>Assembler | Assembly Technician | Fabricator | Line Assembler | Mechanical Assembler | Product Assembler | Production Assembler | Subassembly Assembler | Bench Assembler | Component Assembler</t>
+  </si>
+  <si>
+    <t>Supervisory control and data acquisition SCADA software | Programmable logic controller PLC software | Statistical process control SPC software | Materials requirement planning MRP software | Computerized maintenance management system CMMS | Microsoft Excel | Microsoft Word | Email software | Inventory management systems | Enterprise resource planning ERP system | Database software | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mechanical | English Language | Mathematics | Engineering and Technology | Design | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Team Assemblers | Electrical and Electronic Equipment Assemblers | Electromechanical Equipment Assemblers | Engine and Other Machine Assemblers | Structural Metal Fabricators and Fitters | Fiberglass Laminators and Fabricators | Coil Winders, Tapers, and Finishers | Timing Device Assemblers and Adjusters | Aircraft Structure, Surfaces, Rigging, and Systems Assemblers | Inspectors, Testers, Sorters, Samplers, and Weighers | Machinists | Welders, Cutters, Solderers, and Brazers | Helpers--Production Workers | Production Workers, All Other | First-Line Supervisors of Production and Operating Workers | Industrial Machinery Mechanics | Packaging and Filling Machine Operators and Tenders | Computer Numerically Controlled Tool Operators | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Semiconductor Processing Technicians</t>
+  </si>
+  <si>
+    <t>All assemblers and fabricators not listed separately.</t>
+  </si>
+  <si>
+    <t>Assemble and fabricate products in specialties not classified separately. | Read blueprints, work orders, and assembly instructions to determine requirements. | Position, align, and fasten parts using hand tools, power tools, and fixtures. | Verify dimensions and fit of components using gauges and measuring instruments. | Inspect finished assemblies for defects, completeness, and workmanship. | Adjust or rework assemblies that do not meet specifications. | Operate presses, riveters, soldering equipment, and assembly machinery. | Record production counts, defects, and time on production records. | Maintain a clean, organized, and safe work station. | Perform routine maintenance and setup changes on assembly equipment. | Follow quality standards, work instructions, and safety procedures. | Package, label, and stage completed products for shipment or further processing. | Report material shortages, tooling problems, and quality concerns. | Train and assist new assemblers on procedures and equipment.</t>
+  </si>
+  <si>
+    <t>51-3011.00</t>
+  </si>
+  <si>
+    <t>Bakers</t>
+  </si>
+  <si>
+    <t>Baker | Cake Decorator | Dough Mixer | Mixer | Pastry Chef | Scaler</t>
+  </si>
+  <si>
+    <t>ADP Enterprise eTIME | Afcom Datasafe Computer Services FlexiBake | At Your Service Software CostGuard | Axxya Systems Nutritionist Pro | Barrington Software CookenPro | Culinary Software Services ChefTec | EGS CALCMENU | Email software | Enggist &amp; Grandjean EGS F&amp;B Control | LegacyUSA BakeSmart | Masters Software CakeBoss | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Sage 100 ERP | SoftCafe MenuPro | SweetWARE SmallPICS | SweetWARE nutraCoster Professional | SweetWARE stockCoster | TwinPeaks Software Visual Z-Bake | Web browser software | iPro</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Active Learning | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Customer and Personal Service | Food Production | English Language | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Speech Recognition | Visual Color Discrimination | Problem Sensitivity | Oral Expression | Information Ordering | Deductive Reasoning | Written Comprehension | Speech Clarity | Control Precision | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Perceptual Speed | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | Spend Time Standing | Time Pressure | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Freedom to Make Decisions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Exposed to Minor Burns, Cuts, Bites, or Stings | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Restaurant | Cooks, Short Order | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Fast Food and Counter Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Machine Feeders and Offbearers | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders</t>
+  </si>
+  <si>
+    <t>Mix and bake ingredients to produce breads, rolls, cookies, cakes, pies, pastries, or other baked goods.</t>
+  </si>
+  <si>
+    <t>Adapt the quantity of ingredients to match the amount of items to be baked. | Apply glazes, icings, or other toppings to baked goods, using spatulas or brushes. | Check equipment to ensure that it meets health and safety regulations, and perform maintenance or cleaning, as necessary. | Check products for quality, and identify damaged or expired goods. | Check the quality of raw materials to ensure that standards and specifications are met. | Combine measured ingredients in bowls of mixing, blending, or cooking machinery. | Decorate baked goods, such as cakes or pastries. | Develop new recipes for baked goods. | Direct or coordinate bakery deliveries. | Measure or weigh flour or other ingredients to prepare batters, doughs, fillings, or icings, using scales or graduated containers. | Observe color of products being baked, and adjust oven temperatures, humidity, or conveyor speeds accordingly. | Operate slicing or wrapping machines. | Order or receive supplies or equipment. | Place dough in pans, molds, or on sheets, and bake in production ovens or on grills. | Prepare or maintain inventory or production records. | Roll, knead, cut, or shape dough to form sweet rolls, pie crusts, tarts, cookies, or other products. | Set oven temperatures, and place items into hot ovens for baking. | Set time and speed controls for mixing machines, blending machines, or steam kettles so that ingredients will be mixed or cooked according to instructions.</t>
+  </si>
+  <si>
+    <t>51-3021.00</t>
+  </si>
+  <si>
+    <t>Butchers and Meat Cutters</t>
+  </si>
+  <si>
+    <t>Butcher | Meat Clerk | Meat Cutter | Meat Specialist | Meat Wrapper</t>
+  </si>
+  <si>
+    <t>Financial accounting software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | Production and Processing | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Arm-Hand Steadiness | Control Precision | Category Flexibility | Information Ordering | Problem Sensitivity | Oral Expression | Oral Comprehension | Selective Attention | Trunk Strength | Finger Dexterity | Speech Clarity | Speech Recognition | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Equipment | Spend Time Making Repetitive Motions | Exposed to Very Hot or Cold Temperatures | Time Pressure | Physical Proximity | Frequency of Decision Making | Importance of Being Exact or Accurate | Health and Safety of Other Workers | Consequence of Error | Dealing With Unpleasant, Angry, or Discourteous People | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Pace Determined by Speed of Equipment | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Bending or Twisting Your Body</t>
+  </si>
+  <si>
+    <t>Bakers | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Scientists and Technologists | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers | Packers and Packagers, Hand | Slaughterers and Meat Packers</t>
+  </si>
+  <si>
+    <t>Cut, trim, or prepare consumer-sized portions of meat for use or sale in retail establishments.</t>
+  </si>
+  <si>
+    <t>Cure, smoke, tenderize, and preserve meat. | Cut, trim, bone, tie, and grind meats, such as beef, pork, poultry, and fish, to prepare in cooking form. | Estimate requirements and order or requisition meat supplies to maintain inventories. | Negotiate with representatives from supply companies to determine order details. | Prepare and place meat cuts and products in display counter to appear attractive and catch the shopper's eye. | Prepare special cuts of meat ordered by customers. | Receive, inspect, and store meat upon delivery to ensure meat quality. | Record quantity of meat received and issued to cooks or keep records of meat sales. | Shape, lace, and tie roasts, using boning knife, skewer, and twine. | Supervise other butchers or meat cutters. | Wrap, weigh, label, and price cuts of meat.</t>
+  </si>
+  <si>
+    <t>51-3022.00</t>
+  </si>
+  <si>
+    <t>Meat, Poultry, and Fish Cutters and Trimmers</t>
+  </si>
+  <si>
+    <t>Beef Trimmer | Breast Trimmer | Chicken Cutter | Deboner | Fish Processor | Meat Cutter | Meat Trimmer | Seafood Processor | Trimmer | Wing Scorer</t>
+  </si>
+  <si>
+    <t>Meat inventory software | Microsoft Excel | Sales software | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Monitoring | Critical Thinking | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Food Production | Public Safety and Security | Mathematics | Administration and Management | Mechanical | Personnel and Human Resources | Transportation | Education and Training</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Near Vision | Trunk Strength | Manual Dexterity | Selective Attention | Oral Expression | Multilimb Coordination | Finger Dexterity | Visualization | Information Ordering | Problem Sensitivity | Oral Comprehension | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Importance of Being Exact or Accurate | Physical Proximity | Work With or Contribute to a Work Group or Team | Exposed to Very Hot or Cold Temperatures | Pace Determined by Speed of Equipment | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Bending or Twisting Your Body | Coordinate or Lead Others in Accomplishing Work Activities | Face-to-Face Discussions with Individuals and Within Teams | Work Outcomes and Results of Other Workers | Consequence of Error | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Bakers | Butchers and Meat Cutters | Cooks, Restaurant | Cooks, Short Order | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutters and Trimmers, Hand | Cutting and Slicing Machine Setters, Operators, and Tenders | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Farmworkers, Farm, Ranch, and Aquacultural Animals | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Laborers and Freight, Stock, and Material Movers, Hand | Machine Feeders and Offbearers | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Slaughterers and Meat Packers</t>
+  </si>
+  <si>
+    <t>Use hands or hand tools to perform routine cutting and trimming of meat, poultry, and seafood.</t>
+  </si>
+  <si>
+    <t>Clean and salt hides. | Clean, trim, slice, and section carcasses for future processing. | Cut and trim meat to prepare for packing. | Inspect meat products for defects, bruises or blemishes and remove them along with any excess fat. | Obtain and distribute specified meat or carcass. | Prepare ready-to-heat foods by filleting meat or fish or cutting it into bite-sized pieces, preparing and adding vegetables or applying sauces or breading. | Process primal parts into cuts that are ready for retail use. | Produce hamburger meat and meat trimmings. | Remove parts, such as skin, feathers, scales or bones, from carcass. | Separate meats and byproducts into specified containers and seal containers. | Use knives, cleavers, meat saws, bandsaws, or other equipment to perform meat cutting and trimming. | Weigh meats and tag containers for weight and contents.</t>
+  </si>
+  <si>
+    <t>51-3023.00</t>
+  </si>
+  <si>
+    <t>Slaughterers and Meat Packers</t>
+  </si>
+  <si>
+    <t>Boning Room Worker | Meat Packager | Meat Packer | Meat Processor | Meat Wrapper | Saw Man | Side Puller | Wrapper</t>
+  </si>
+  <si>
+    <t>AccountMate Software AccountMate | AgInfoLink Meat Inventory Tracking System MITS | Integrated Management Systems Food Connex Cloud | Microsoft Excel | Microsoft Office software | RFID software | Second Foundation NaviMeat | Traceability software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | Production and Processing | English Language</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Near Vision | Trunk Strength | Static Strength | Control Precision | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Spend Time Standing | Spend Time Making Repetitive Motions | Pace Determined by Speed of Equipment | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Health and Safety of Other Workers | Physical Proximity | Importance of Being Exact or Accurate | Exposed to Minor Burns, Cuts, Bites, or Stings | Coordinate or Lead Others in Accomplishing Work Activities | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Animal Breeders | Animal Scientists | Bakers | Butchers and Meat Cutters | Cooks, Institution and Cafeteria | Cooks, Restaurant | Cooks, Short Order | Cutting and Slicing Machine Setters, Operators, and Tenders | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Farmworkers, Farm, Ranch, and Aquacultural Animals | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Scientists and Technologists | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand</t>
+  </si>
+  <si>
+    <t>Perform nonroutine or precision functions involving the preparation of large portions of meat. Work may include specialized slaughtering tasks, cutting standard or premium cuts of meat for marketing, making sausage, or wrapping meats. Work typically occurs in slaughtering, meat packing, or wholesale establishments.</t>
+  </si>
+  <si>
+    <t>Cut, trim, skin, sort, and wash viscera of slaughtered animals to separate edible portions from offal. | Grind meat into hamburger, and into trimmings used to prepare sausages, luncheon meats, and other meat products. | Remove bones, and cut meat into standard cuts in preparation for marketing. | Saw, split, or scribe carcasses into smaller portions to facilitate handling. | Sever jugular veins to drain blood and facilitate slaughtering. | Shackle hind legs of animals to raise them for slaughtering or skinning. | Shave or singe and defeather carcasses, and wash them in preparation for further processing or packaging. | Skin sections of animals or whole animals. | Slit open, eviscerate, and trim carcasses of slaughtered animals. | Stun animals prior to slaughtering. | Tend assembly lines, performing a few of the many cuts needed to process a carcass. | Trim head meat, and sever or remove parts of animals' heads or skulls. | Trim, clean, or cure animal hides. | Wrap dressed carcasses or meat cuts.</t>
+  </si>
+  <si>
+    <t>51-3091.00</t>
+  </si>
+  <si>
+    <t>Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Bean Roaster | Coffee Roaster | Line Operator | Machine Operator | Oven Operator | Oven Technician | Roast Master | Roaster | Roaster Operator | Roasterman</t>
+  </si>
+  <si>
+    <t>Email software | Microsoft Excel</t>
+  </si>
+  <si>
+    <t>Monitoring | Critical Thinking | Reading Comprehension | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | English Language | Public Safety and Security | Food Production</t>
+  </si>
+  <si>
+    <t>Near Vision | Problem Sensitivity | Speech Recognition | Control Precision | Arm-Hand Steadiness | Selective Attention | Perceptual Speed | Category Flexibility | Information Ordering | Oral Comprehension | Visual Color Discrimination | Trunk Strength | Rate Control | Multilimb Coordination | Finger Dexterity | Manual Dexterity | Flexibility of Closure | Written Expression | Oral Expression | Speech Clarity | Auditory Attention | Hearing Sensitivity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Not Environmentally Controlled | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Time Pressure | Exposed to Very Hot or Cold Temperatures | Contact With Others | Pace Determined by Speed of Equipment | Consequence of Error | Work With or Contribute to a Work Group or Team | Importance of Repeating Same Tasks | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Bakers | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Conveyor Operators and Tenders | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Batchmakers | Food Cooking Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Graders and Sorters, Agricultural Products | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend food or tobacco roasting, baking, or drying equipment, including hearth ovens, kiln driers, roasters, char kilns, and vacuum drying equipment.</t>
+  </si>
+  <si>
+    <t>Clean equipment with steam, hot water, and hoses. | Clear or dislodge blockages in bins, screens, or other equipment, using poles, brushes, or mallets. | Fill or remove product from trays, carts, hoppers, or equipment, using scoops, peels, or shovels, or by hand. | Install equipment, such as spray units, cutting blades, or screens, using hand tools. | Observe flow of materials and listen for machine malfunctions, such as jamming or spillage, and notify supervisors if corrective actions fail. | Observe temperature, humidity, pressure gauges, and product samples and adjust controls, such as thermostats and valves, to maintain prescribed operating conditions for specific stages. | Observe, feel, taste, or otherwise examine products during and after processing to ensure conformance to standards. | Open valves, gates, or chutes or use shovels to load or remove products from ovens or other equipment. | Operate or tend equipment that roasts, bakes, dries, or cures food items such as cocoa and coffee beans, grains, nuts, and bakery products. | Push racks or carts to transfer products to storage, cooling stations, or the next stage of processing. | Read work orders to determine quantities and types of products to be baked, dried, or roasted. | Record production data, such as weight and amount of product processed, type of product, and time and temperature of processing. | Set temperature and time controls, light ovens, burners, driers, or roasters, and start equipment, such as conveyors, cylinders, blowers, driers, or pumps. | Signal coworkers to synchronize flow of materials. | Smooth out products in bins, pans, trays, or conveyors, using rakes or shovels. | Start conveyors to move roasted grain to cooling pans and agitate grain with rakes as blowers force air through perforated bottoms of pans. | Take product samples during or after processing for laboratory analyses. | Test products for moisture content, using moisture meters. | Weigh or measure products, using scale hoppers or scale conveyors.</t>
+  </si>
+  <si>
+    <t>51-3092.00</t>
+  </si>
+  <si>
+    <t>Food Batchmakers</t>
+  </si>
+  <si>
+    <t>Batching Operator | Blender | Brewing Technician | Compounder | Dosier Operator | Dough Scaler | Mix Technician | Mixer | Mixer Operator | Syrup Maker</t>
+  </si>
+  <si>
+    <t>Edible Software | Microsoft Office software | Plex Systems Plex Manufacturing Cloud</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Food Production | Production and Processing | Education and Training | English Language | Mechanical | Administration and Management | Mathematics | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Information Ordering | Near Vision | Oral Comprehension | Control Precision | Problem Sensitivity | Written Comprehension | Category Flexibility | Oral Expression | Speech Recognition | Auditory Attention | Manual Dexterity | Selective Attention | Perceptual Speed</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Pace Determined by Speed of Equipment | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Time Pressure | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Physical Proximity | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Freedom to Make Decisions | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Bakers | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooks, Restaurant | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Cooking Machine Operators and Tenders | Food Science Technicians | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Graders and Sorters, Agricultural Products | Machine Feeders and Offbearers | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Set up and operate equipment that mixes or blends ingredients used in the manufacturing of food products. Includes candy makers and cheese makers.</t>
+  </si>
+  <si>
+    <t>Clean and sterilize vats and factory processing areas. | Cool food product batches on slabs or in water-cooled kettles. | Determine mixing sequences, based on knowledge of temperature effects and of the solubility of specific ingredients. | Examine, feel, and taste product samples during production to evaluate quality, color, texture, flavor, and bouquet, and document the results. | Fill processing or cooking containers, such as kettles, rotating cookers, pressure cookers, or vats, with ingredients, by opening valves, by starting pumps or injectors, or by hand. | Follow recipes to produce food products of specified flavor, texture, clarity, bouquet, or color. | Formulate or modify recipes for specific kinds of food products. | Give directions to other workers who are assisting in the batchmaking process. | Grade food products according to government regulations or according to type, color, bouquet, and moisture content. | Homogenize or pasteurize material to prevent separation or to obtain prescribed butterfat content, using a homogenizing device. | Inspect and pack the final product. | Inspect vats after cleaning to ensure that fermentable residue has been removed. | Manipulate products, by hand or using machines, to separate, spread, knead, spin, cast, cut, pull, or roll products. | Mix or blend ingredients, according to recipes, using a paddle or an agitator, or by controlling vats that heat and mix ingredients. | Modify cooking and forming operations based on the results of sampling processes, adjusting time cycles and ingredients to achieve desired qualities, such as firmness or texture. | Observe and listen to equipment to detect possible malfunctions, such as leaks or plugging, and report malfunctions or undesirable tastes to supervisors. | Observe gauges and thermometers to determine if the mixing chamber temperature is within specified limits, and turn valves to control the temperature. | Operate refining machines to reduce the particle size of cooked batches. | Place products on carts or conveyors to transfer them to the next stage of processing. | Press switches and turn knobs to start, adjust, and regulate equipment, such as beaters, extruders, discharge pipes, and salt pumps. | Record production and test data for each food product batch, such as the ingredients used, temperature, test results, and time cycle. | Select and measure or weigh ingredients, using English or metric measures and balance scales. | Set up, operate, and tend equipment that cooks, mixes, blends, or processes ingredients in the manufacturing of food products, according to formulas or recipes. | Test food product samples for moisture content, acidity level, specific gravity, or butter-fat content, and continue processing until desired levels are reached. | Turn valve controls to start equipment and to adjust operation to maintain product quality.</t>
+  </si>
+  <si>
+    <t>51-3093.00</t>
+  </si>
+  <si>
+    <t>Food Cooking Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Cooker Operator | Food Production Worker | Fryer Operator | Kettle Fry Cook Operator | Machine Operator | Mogul Operator | Oven Operator | Peeler Operator | Retort Operator | Thermo Processor</t>
+  </si>
+  <si>
+    <t>Database software</t>
+  </si>
+  <si>
+    <t>Production and Processing | Food Production | Administration and Management | Education and Training | Mechanical</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Written Comprehension | Oral Comprehension | Near Vision | Control Precision | Selective Attention | Information Ordering | Manual Dexterity | Arm-Hand Steadiness | Reaction Time | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Freedom to Make Decisions | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Spend Time Walking or Running | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | Spend Time Standing | Physical Proximity | Importance of Being Exact or Accurate | Consequence of Error | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Health and Safety of Other Workers | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Bakers | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooks, Restaurant | Cooling and Freezing Equipment Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Food Batchmakers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Furnace, Kiln, Oven, Drier, and Kettle Operators and Tenders | Graders and Sorters, Agricultural Products | Heat Treating Equipment Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Metal-Refining Furnace Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Textile Bleaching and Dyeing Machine Operators and Tenders</t>
+  </si>
+  <si>
+    <t>Operate or tend cooking equipment, such as steam cooking vats, deep fry cookers, pressure cookers, kettles, and boilers, to prepare food products.</t>
+  </si>
+  <si>
+    <t>Activate agitators and paddles to mix or stir ingredients, stopping machines when ingredients are thoroughly mixed. | Admit required amounts of water, steam, cooking oils, or compressed air into equipment, such as by opening water valves to cool mixtures to the desired consistency. | Clean, wash, and sterilize equipment and cooking area, using water hoses, cleaning or sterilizing solutions, or rinses. | Collect and examine product samples during production to test them for quality, color, content, consistency, viscosity, acidity, or specific gravity. | Listen for malfunction alarms, and shut down equipment and notify supervisors when necessary. | Measure or weigh ingredients, using scales or measuring containers. | Notify or signal other workers to operate equipment or when processing is complete. | Observe gauges, dials, and product characteristics, and adjust controls to maintain appropriate temperature, pressure, and flow of ingredients. | Operate auxiliary machines and equipment, such as grinders, canners, and molding presses, to prepare or further process products. | Place products on conveyors or carts, and monitor product flow. | Pour, dump, or load prescribed quantities of ingredients or products into cooking equipment, manually or using a hoist. | Read work orders, recipes, or formulas to determine cooking times and temperatures, and ingredient specifications. | Record production and test data, such as processing steps, temperature and steam readings, cooking time, batches processed, and test results. | Remove cooked material or products from equipment. | Set temperature, pressure, and time controls, and start conveyers, machines, or pumps. | Tend or operate and control equipment, such as kettles, cookers, vats and tanks, and boilers, to cook ingredients or prepare products for further processing. | Turn valves or start pumps to add ingredients or drain products from equipment and to transfer products for storage, cooling, or further processing.</t>
+  </si>
+  <si>
+    <t>51-3099.00</t>
+  </si>
+  <si>
+    <t>Food Processing Workers, All Other</t>
+  </si>
+  <si>
+    <t>Cheese Maker | Food Processing Worker | Food Production Worker | Ingredient Handler | Poultry Processing Worker | Produce Processor | Seafood Processor | Dairy Processing Worker | Food Plant Operator | Beverage Processing Worker</t>
+  </si>
+  <si>
+    <t>Food Production | Production and Processing | English Language | Chemistry | Mechanical | Public Safety and Security | Mathematics</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Bending or Twisting Your Body | Physical Proximity | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Consequence of Error | Degree of Automation | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Food Batchmakers | Bakers | Butchers and Meat Cutters | Meat, Poultry, and Fish Cutters and Trimmers | Slaughterers and Meat Packers | Food Cooking Machine Operators and Tenders | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Packaging and Filling Machine Operators and Tenders | Mixing and Blending Machine Setters, Operators, and Tenders | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Cooling and Freezing Equipment Operators and Tenders | Inspectors, Testers, Sorters, Samplers, and Weighers | Graders and Sorters, Agricultural Products | Helpers--Production Workers | Production Workers, All Other | First-Line Supervisors of Production and Operating Workers | Food Science Technicians | Food Scientists and Technologists | Industrial Machinery Mechanics | Packers and Packagers, Hand</t>
+  </si>
+  <si>
+    <t>All food processing workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Process food products in roles not classified separately. | Operate and tend equipment that washes, cuts, mixes, cooks, or packages food. | Measure, weigh, and combine ingredients according to formulas and recipes. | Monitor processing temperatures, times, pressures, and flow rates. | Inspect raw materials and finished products for quality and contamination. | Sort, trim, and grade food products according to specifications. | Clean and sanitize equipment, utensils, and processing areas. | Record production quantities, batch data, and quality measurements. | Follow food safety, sanitation, and hazard analysis requirements. | Package, label, date, and stage products for storage or shipment. | Adjust machine settings to maintain product consistency. | Report equipment malfunctions and assist with minor repairs. | Handle and store ingredients under proper temperature and humidity conditions. | Dispose of waste, trimmings, and byproducts according to procedures.</t>
+  </si>
+  <si>
+    <t>51-4021.00</t>
+  </si>
+  <si>
+    <t>Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Equipment Technician | Extruder Operator | Extrusion Operator | Extrusion Press Operator | Machine Operator | Metal Inspector | Setup Operator | Wire Mill Operator | Wire Mill Rover</t>
+  </si>
+  <si>
+    <t>Enterprise application integration EAI software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Operational databases | SAP software</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Control Precision | Multilimb Coordination | Reaction Time | Manual Dexterity | Problem Sensitivity | Near Vision | Rate Control | Trunk Strength | Static Strength | Arm-Hand Steadiness | Flexibility of Closure | Information Ordering | Perceptual Speed | Deductive Reasoning | Oral Comprehension | Finger Dexterity | Selective Attention | Visualization | Speech Clarity | Speech Recognition | Auditory Attention | Visual Color Discrimination | Far Vision | Stamina</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Pace Determined by Speed of Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Spend Time Standing | Time Pressure | Impact of Decisions on Co-workers or Company Results | Exposed to Contaminants | Consequence of Error | Spend Time Walking or Running | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Hazardous Equipment | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines to extrude or draw thermoplastic or metal materials into tubes, rods, hoses, wire, bars, or structural shapes.</t>
+  </si>
+  <si>
+    <t>Adjust controls to draw or press metal into specified shapes and diameters. | Change dies on extruding machines, according to production line changes. | Clean work areas. | Determine setup procedures and select machine dies and parts, according to specifications. | Install dies, machine screws, and sizing rings on machines that extrude thermoplastic or metal materials. | Load machine hoppers with mixed materials, using augers, or stuff rolls of plastic dough into machine cylinders. | Maintain an inventory of materials. | Measure and examine extruded products to locate defects and to check for conformance to specifications, adjusting controls as necessary to alter products. | Operate shearing mechanisms to cut rods to specified lengths. | Reel extruded products into rolls of specified lengths and weights. | Replace worn dies when products vary from specifications. | Select nozzles, spacers, and wire guides, according to diameters and lengths of rods. | Start machines and set controls to regulate vacuum, air pressure, sizing rings, and temperature, and to synchronize speed of extrusion. | Test physical properties of products with testing devices such as acid-bath testers, burst testers, and impact testers. | Troubleshoot, maintain, and make minor repairs to equipment. | Weigh and mix pelletized, granular, or powdered thermoplastic materials and coloring pigments.</t>
+  </si>
+  <si>
+    <t>51-4022.00</t>
+  </si>
+  <si>
+    <t>Forging Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Blacksmith | Cold Header Operator | Forge Operator | Forge Press Operator | Forger | Hammer Operator | Header Set-Up Operator | Machine Operator | Process Technician | Set Up Technician</t>
+  </si>
+  <si>
+    <t>Email software | Inventory tracking software | Machine control software</t>
+  </si>
+  <si>
+    <t>Monitoring | Reading Comprehension | Active Listening</t>
+  </si>
+  <si>
+    <t>Production and Processing | Mathematics | Education and Training | Mechanical | Engineering and Technology | Design</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Written Comprehension | Oral Expression | Problem Sensitivity | Information Ordering | Arm-Hand Steadiness | Control Precision | Reaction Time | Manual Dexterity | Selective Attention | Visualization | Perceptual Speed | Inductive Reasoning | Deductive Reasoning | Auditory Attention | Rate Control | Multilimb Coordination | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Standing | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | In an Open Vehicle or Operating Equipment | Pace Determined by Speed of Equipment | Importance of Being Exact or Accurate | Exposed to Very Hot or Cold Temperatures | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Frequency of Decision Making | Indoors, Not Environmentally Controlled | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Consequence of Error | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Maintenance Workers, Machinery | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Welding, Soldering, and Brazing Machine Setters, Operators, and Tenders | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend forging machines to taper, shape, or form metal or plastic parts.</t>
+  </si>
+  <si>
+    <t>Confer with other workers about machine setups and operational specifications. | Install, adjust, and remove dies, synchronizing cams, forging hammers, and stop guides, using overhead cranes or other hoisting devices, and hand tools. | Measure and inspect machined parts to ensure conformance to product specifications. | Position and move metal wires or workpieces through a series of dies that compress and shape stock to form die impressions. | Read work orders or blueprints to determine specified tolerances and sequences of operations for machine setup. | Remove dies from machines when production runs are finished. | Repair, maintain, and replace parts on dies. | Select, align, and bolt positioning fixtures, stops, and specified dies to rams and anvils, forging rolls, or presses and hammers. | Set up, operate, or tend presses and forging machines to perform hot or cold forging by flattening, straightening, bending, cutting, piercing, or other operations to taper, shape, or form metal. | Sharpen cutting tools and drill bits, using bench grinders. | Start machines to produce sample workpieces, and observe operations to detect machine malfunctions and to verify that machine setups conform to specifications. | Trim and compress finished forgings to specified tolerances. | Turn handles or knobs to set pressures and depths of ram strokes and to synchronize machine operations.</t>
+  </si>
+  <si>
+    <t>51-4023.00</t>
+  </si>
+  <si>
+    <t>Rolling Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Breakdown Mill Operator | Calender Operator | Cold Mill Operator | Machine Operator | Mill Operator | Rolling Mill Operator | Roughing Mill Operator | Temper Mill Operator | Tube Mill Operator | Weld Mill Operator</t>
+  </si>
+  <si>
+    <t>Email software | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Critical Thinking | Active Learning | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Mechanical | Production and Processing | English Language | Education and Training</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Control Precision | Reaction Time | Near Vision | Rate Control | Manual Dexterity | Multilimb Coordination | Arm-Hand Steadiness | Deductive Reasoning | Information Ordering | Perceptual Speed | Finger Dexterity | Response Orientation | Static Strength | Oral Expression | Speech Clarity | Speech Recognition | Auditory Attention | Far Vision | Trunk Strength | Selective Attention | Inductive Reasoning | Written Comprehension | Oral Comprehension | Visualization | Flexibility of Closure | Depth Perception | Stamina</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Contact With Others | Time Pressure | Spend Time Standing | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Pace Determined by Speed of Equipment | Health and Safety of Other Workers | Exposed to Contaminants | Frequency of Decision Making | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Equipment | Spend Time Walking or Running | Determine Tasks, Priorities and Goals | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Exposed to Minor Burns, Cuts, Bites, or Stings | Work Outcomes and Results of Other Workers | Indoors, Not Environmentally Controlled | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Molding, Coremaking, and Casting Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines to roll steel or plastic forming bends, beads, knurls, rolls, or plate, or to flatten, temper, or reduce gauge of material.</t>
+  </si>
+  <si>
+    <t>Activate shears and grinders to trim workpieces. | Adjust and correct machine set-ups to reduce thicknesses, reshape products, and eliminate product defects. | Calculate draft space and roll speed for each mill stand to plan rolling sequences and specified dimensions and tempers. | Direct and train other workers to change rolls, operate mill equipment, remove coils and cobbles, and band and load material. | Disassemble sizing mills removed from rolling lines, and sort and store parts. | Examine, inspect, and measure raw materials and finished products to verify conformance to specifications. | Fill oil cups, adjust valves, and observe gauges to control flow of metal coolants and lubricants onto workpieces. | Install equipment such as guides, guards, gears, cooling equipment, and rolls, using hand tools. | Manipulate controls and observe dial indicators to monitor, adjust, and regulate speeds of machine mechanisms. | Monitor machine cycles and mill operation to detect jamming and to ensure that products conform to specifications. | Position, align, and secure arbors, spindles, coils, mandrels, dies, and slitting knives. | Read rolling orders, blueprints, and mill schedules to determine setup specifications, work sequences, product dimensions, and installation procedures. | Record mill production on schedule sheets. | Remove scratches and polish roll surfaces, using polishing stones and electric buffers. | Select rolls, dies, roll stands, and chucks from data charts to form specified contours and to fabricate products. | Set distance points between rolls, guides, meters, and stops, according to specifications. | Signal and assist other workers to remove and position equipment, fill hoppers, and feed materials into machines. | Start operation of rolling and milling machines to flatten, temper, form, and reduce sheet metal sections and to produce steel strips. | Thread or feed sheets or rods through rolling mechanisms, or start and control mechanisms that automatically feed steel into rollers.</t>
+  </si>
+  <si>
+    <t>51-4031.00</t>
+  </si>
+  <si>
+    <t>Cutting, Punching, and Press Machine Setters, Operators, and Tenders, Metal and Plastic</t>
+  </si>
+  <si>
+    <t>Die Setter | Fabrication Operator | Machine Operator | Machine Setter | Press Brake Operator | Press Operator | Punch Press Operator | Saw Operator | Setup Operator | Slitter Operator</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Automated inventory software | Computerized numerical control CNC software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Operational databases | SAP software | Striker Systems SS-Punch</t>
+  </si>
+  <si>
+    <t>Production and Processing</t>
+  </si>
+  <si>
+    <t>Arm-Hand Steadiness | Control Precision | Near Vision | Information Ordering | Manual Dexterity | Reaction Time | Selective Attention | Written Comprehension | Oral Comprehension | Visualization | Perceptual Speed | Flexibility of Closure | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Oral Expression | Speech Clarity | Speech Recognition | Depth Perception | Far Vision | Trunk Strength | Static Strength | Rate Control | Multilimb Coordination | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Contaminants | Pace Determined by Speed of Equipment | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Exposed to Hazardous Equipment | Time Pressure | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Minor Burns, Cuts, Bites, or Stings | Indoors, Not Environmentally Controlled | Spend Time Standing | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Adhesive Bonding Machine Operators and Tenders | Cutting and Slicing Machine Setters, Operators, and Tenders | Drilling and Boring Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Extruding and Drawing Machine Setters, Operators, and Tenders, Metal and Plastic | Extruding, Forming, Pressing, and Compacting Machine Setters, Operators, and Tenders | Forging Machine Setters, Operators, and Tenders, Metal and Plastic | Grinding and Polishing Workers, Hand | Grinding, Lapping, Polishing, and Buffing Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Industrial Machinery Mechanics | Lathe and Turning Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Machine Feeders and Offbearers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Multiple Machine Tool Setters, Operators, and Tenders, Metal and Plastic | Paper Goods Machine Setters, Operators, and Tenders | Rolling Machine Setters, Operators, and Tenders, Metal and Plastic | Sawing Machine Setters, Operators, and Tenders, Wood | Textile Cutting Machine Setters, Operators, and Tenders | Tool Grinders, Filers, and Sharpeners | Tool and Die Makers | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Set up, operate, or tend machines to saw, cut, shear, slit, punch, crimp, notch, bend, or straighten metal or plastic material.</t>
+  </si>
+  <si>
+    <t>Adjust ram strokes of presses to specified lengths, using hand tools. | Clean and lubricate machines. | Clean work area. | Examine completed workpieces for defects, such as chipped edges or marred surfaces and sort defective pieces according to types of flaws. | Grind out burrs or sharp edges, using portable grinders, speed lathes, or polishing jacks. | Hone cutters with oilstones to remove nicks. | Install, align, and lock specified punches, dies, cutting blades, or other fixtures in rams or beds of machines, using gauges, templates, feelers, shims, and hand tools. | Load workpieces, plastic material, or chemical solutions into machines. | Lubricate workpieces with oil. | Mark identifying data on workpieces. | Measure completed workpieces to verify conformance to specifications, using micrometers, gauges, calipers, templates, or rulers. | Operate forklifts to deliver materials. | Place workpieces on cutting tables, manually or using hoists, cranes, or sledges. | Plan sequences of operations, applying knowledge of physical properties of workpiece materials. | Position guides, stops, holding blocks, or other fixtures to secure and direct workpieces, using hand tools and measuring devices. | Position, align, and secure workpieces against fixtures or stops on machine beds or on dies. | Preheat workpieces, using heating furnaces or hand torches. | Read work orders or production schedules to determine specifications, such as materials to be used, locations of cutting lines, or dimensions and tolerances. | Remove housings, feed tubes, tool holders, or other accessories to replace worn or broken parts, such as springs or bushings. | Replace defective blades or wheels, using hand tools. | Scribe reference lines on workpieces as guides for cutting operations, according to blueprints, templates, sample parts, or specifications. | Select, clean, and install spacers, rubber sleeves, or cutters on arbors. | Set blade tensions, heights, and angles to perform prescribed cuts, using wrenches. | Set stops on machine beds, change dies, and adjust components, such as rams or power presses, when making multiple or successive passes. | Set up, operate, or tend machines to saw, cut, shear, slit, punch, crimp, notch, bend, or straighten metal or plastic material. | Sharpen dulled blades, using bench grinders, abrasive wheels, or lathes. | Start machines, monitor their operations, and record operational data. | Test and adjust machine speeds or actions, according to product specifications, using gauges and hand tools. | Turn controls to set cutting speeds, feed rates, or table angles for specified operations. | Turn valves to start flow of coolant against cutting areas or to start airflow that blows cuttings away from kerfs. | Use equipment designed to join sheet metal, such as spot welders.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1961,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I11" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H13" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J14" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" t="s">
+        <v>167</v>
+      </c>
+      <c r="E16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H17" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" t="s">
+        <v>183</v>
+      </c>
+      <c r="J17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G18" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" t="s">
+        <v>205</v>
+      </c>
+      <c r="J19" t="s">
+        <v>206</v>
+      </c>
+      <c r="K19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F20" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H20" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" t="s">
+        <v>216</v>
+      </c>
+      <c r="J20" t="s">
+        <v>217</v>
+      </c>
+      <c r="K20" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" t="s">
+        <v>224</v>
+      </c>
+      <c r="G21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H21" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" t="s">
+        <v>227</v>
+      </c>
+      <c r="J21" t="s">
+        <v>228</v>
+      </c>
+      <c r="K21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" t="s">
+        <v>235</v>
+      </c>
+      <c r="G22" t="s">
+        <v>236</v>
+      </c>
+      <c r="H22" t="s">
+        <v>237</v>
+      </c>
+      <c r="I22" t="s">
+        <v>238</v>
+      </c>
+      <c r="J22" t="s">
+        <v>239</v>
+      </c>
+      <c r="K22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B23" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" t="s">
+        <v>243</v>
+      </c>
+      <c r="D23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F23" t="s">
+        <v>246</v>
+      </c>
+      <c r="G23" t="s">
+        <v>247</v>
+      </c>
+      <c r="H23" t="s">
+        <v>248</v>
+      </c>
+      <c r="I23" t="s">
+        <v>249</v>
+      </c>
+      <c r="J23" t="s">
+        <v>250</v>
+      </c>
+      <c r="K23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" t="s">
+        <v>256</v>
+      </c>
+      <c r="F24" t="s">
+        <v>257</v>
+      </c>
+      <c r="G24" t="s">
+        <v>258</v>
+      </c>
+      <c r="H24" t="s">
+        <v>259</v>
+      </c>
+      <c r="I24" t="s">
+        <v>260</v>
+      </c>
+      <c r="J24" t="s">
+        <v>261</v>
+      </c>
+      <c r="K24" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" t="s">
+        <v>267</v>
+      </c>
+      <c r="F25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G25" t="s">
+        <v>269</v>
+      </c>
+      <c r="H25" t="s">
+        <v>270</v>
+      </c>
+      <c r="I25" t="s">
+        <v>271</v>
+      </c>
+      <c r="J25" t="s">
+        <v>272</v>
+      </c>
+      <c r="K25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" t="s">
+        <v>277</v>
+      </c>
+      <c r="E26" t="s">
+        <v>168</v>
+      </c>
+      <c r="F26" t="s">
+        <v>278</v>
+      </c>
+      <c r="G26" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" t="s">
+        <v>279</v>
+      </c>
+      <c r="I26" t="s">
+        <v>280</v>
+      </c>
+      <c r="J26" t="s">
+        <v>281</v>
+      </c>
+      <c r="K26" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" t="s">
+        <v>285</v>
+      </c>
+      <c r="D27" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" t="s">
+        <v>288</v>
+      </c>
+      <c r="G27" t="s">
+        <v>289</v>
+      </c>
+      <c r="H27" t="s">
+        <v>290</v>
+      </c>
+      <c r="I27" t="s">
+        <v>291</v>
+      </c>
+      <c r="J27" t="s">
+        <v>292</v>
+      </c>
+      <c r="K27" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" t="s">
+        <v>295</v>
+      </c>
+      <c r="C28" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" t="s">
+        <v>297</v>
+      </c>
+      <c r="E28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F28" t="s">
+        <v>299</v>
+      </c>
+      <c r="G28" t="s">
+        <v>300</v>
+      </c>
+      <c r="H28" t="s">
+        <v>301</v>
+      </c>
+      <c r="I28" t="s">
+        <v>302</v>
+      </c>
+      <c r="J28" t="s">
+        <v>303</v>
+      </c>
+      <c r="K28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B29" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E29" t="s">
+        <v>309</v>
+      </c>
+      <c r="F29" t="s">
+        <v>310</v>
+      </c>
+      <c r="G29" t="s">
+        <v>311</v>
+      </c>
+      <c r="H29" t="s">
+        <v>312</v>
+      </c>
+      <c r="I29" t="s">
+        <v>313</v>
+      </c>
+      <c r="J29" t="s">
+        <v>314</v>
+      </c>
+      <c r="K29" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>316</v>
+      </c>
+      <c r="B30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C30" t="s">
+        <v>318</v>
+      </c>
+      <c r="D30" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" t="s">
+        <v>320</v>
+      </c>
+      <c r="F30" t="s">
+        <v>321</v>
+      </c>
+      <c r="G30" t="s">
+        <v>322</v>
+      </c>
+      <c r="H30" t="s">
+        <v>323</v>
+      </c>
+      <c r="I30" t="s">
+        <v>324</v>
+      </c>
+      <c r="J30" t="s">
+        <v>325</v>
+      </c>
+      <c r="K30" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>327</v>
+      </c>
+      <c r="B31" t="s">
+        <v>328</v>
+      </c>
+      <c r="C31" t="s">
+        <v>329</v>
+      </c>
+      <c r="D31" t="s">
+        <v>330</v>
+      </c>
+      <c r="E31" t="s">
+        <v>331</v>
+      </c>
+      <c r="F31" t="s">
+        <v>332</v>
+      </c>
+      <c r="G31" t="s">
+        <v>333</v>
+      </c>
+      <c r="H31" t="s">
+        <v>334</v>
+      </c>
+      <c r="I31" t="s">
+        <v>335</v>
+      </c>
+      <c r="J31" t="s">
+        <v>336</v>
+      </c>
+      <c r="K31" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" t="s">
+        <v>340</v>
+      </c>
+      <c r="D32" t="s">
+        <v>341</v>
+      </c>
+      <c r="E32" t="s">
+        <v>342</v>
+      </c>
+      <c r="F32" t="s">
+        <v>343</v>
+      </c>
+      <c r="G32" t="s">
+        <v>344</v>
+      </c>
+      <c r="H32" t="s">
+        <v>345</v>
+      </c>
+      <c r="I32" t="s">
+        <v>346</v>
+      </c>
+      <c r="J32" t="s">
+        <v>347</v>
+      </c>
+      <c r="K32" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>349</v>
+      </c>
+      <c r="B33" t="s">
+        <v>350</v>
+      </c>
+      <c r="C33" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" t="s">
+        <v>352</v>
+      </c>
+      <c r="E33" t="s">
+        <v>353</v>
+      </c>
+      <c r="F33" t="s">
+        <v>354</v>
+      </c>
+      <c r="G33" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" t="s">
+        <v>356</v>
+      </c>
+      <c r="I33" t="s">
+        <v>357</v>
+      </c>
+      <c r="J33" t="s">
+        <v>358</v>
+      </c>
+      <c r="K33" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" t="s">
+        <v>361</v>
+      </c>
+      <c r="C34" t="s">
+        <v>362</v>
+      </c>
+      <c r="D34" t="s">
+        <v>363</v>
+      </c>
+      <c r="E34" t="s">
+        <v>364</v>
+      </c>
+      <c r="F34" t="s">
+        <v>365</v>
+      </c>
+      <c r="G34" t="s">
+        <v>366</v>
+      </c>
+      <c r="H34" t="s">
+        <v>367</v>
+      </c>
+      <c r="I34" t="s">
+        <v>368</v>
+      </c>
+      <c r="J34" t="s">
+        <v>369</v>
+      </c>
+      <c r="K34" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>371</v>
+      </c>
+      <c r="B35" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" t="s">
+        <v>373</v>
+      </c>
+      <c r="D35" t="s">
+        <v>374</v>
+      </c>
+      <c r="E35" t="s">
+        <v>375</v>
+      </c>
+      <c r="F35" t="s">
+        <v>376</v>
+      </c>
+      <c r="G35" t="s">
+        <v>377</v>
+      </c>
+      <c r="H35" t="s">
+        <v>378</v>
+      </c>
+      <c r="I35" t="s">
+        <v>379</v>
+      </c>
+      <c r="J35" t="s">
+        <v>380</v>
+      </c>
+      <c r="K35" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" t="s">
+        <v>383</v>
+      </c>
+      <c r="C36" t="s">
+        <v>384</v>
+      </c>
+      <c r="D36" t="s">
+        <v>385</v>
+      </c>
+      <c r="E36" t="s">
+        <v>386</v>
+      </c>
+      <c r="F36" t="s">
+        <v>387</v>
+      </c>
+      <c r="G36" t="s">
+        <v>388</v>
+      </c>
+      <c r="H36" t="s">
+        <v>389</v>
+      </c>
+      <c r="I36" t="s">
+        <v>390</v>
+      </c>
+      <c r="J36" t="s">
+        <v>391</v>
+      </c>
+      <c r="K36" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>393</v>
+      </c>
+      <c r="B37" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" t="s">
+        <v>396</v>
+      </c>
+      <c r="E37" t="s">
+        <v>397</v>
+      </c>
+      <c r="F37" t="s">
+        <v>398</v>
+      </c>
+      <c r="G37" t="s">
+        <v>399</v>
+      </c>
+      <c r="H37" t="s">
+        <v>400</v>
+      </c>
+      <c r="I37" t="s">
+        <v>401</v>
+      </c>
+      <c r="J37" t="s">
+        <v>402</v>
+      </c>
+      <c r="K37" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>404</v>
+      </c>
+      <c r="B38" t="s">
+        <v>405</v>
+      </c>
+      <c r="C38" t="s">
+        <v>406</v>
+      </c>
+      <c r="D38" t="s">
+        <v>407</v>
+      </c>
+      <c r="E38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F38" t="s">
+        <v>409</v>
+      </c>
+      <c r="G38" t="s">
+        <v>410</v>
+      </c>
+      <c r="H38" t="s">
+        <v>411</v>
+      </c>
+      <c r="I38" t="s">
+        <v>412</v>
+      </c>
+      <c r="J38" t="s">
+        <v>413</v>
+      </c>
+      <c r="K38" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>415</v>
+      </c>
+      <c r="B39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C39" t="s">
+        <v>417</v>
+      </c>
+      <c r="D39" t="s">
+        <v>418</v>
+      </c>
+      <c r="E39" t="s">
+        <v>419</v>
+      </c>
+      <c r="F39" t="s">
+        <v>420</v>
+      </c>
+      <c r="G39" t="s">
+        <v>421</v>
+      </c>
+      <c r="H39" t="s">
+        <v>422</v>
+      </c>
+      <c r="I39" t="s">
+        <v>423</v>
+      </c>
+      <c r="J39" t="s">
+        <v>424</v>
+      </c>
+      <c r="K39" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>426</v>
+      </c>
+      <c r="B40" t="s">
+        <v>427</v>
+      </c>
+      <c r="C40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D40" t="s">
+        <v>429</v>
+      </c>
+      <c r="E40" t="s">
+        <v>397</v>
+      </c>
+      <c r="F40" t="s">
+        <v>430</v>
+      </c>
+      <c r="G40" t="s">
+        <v>431</v>
+      </c>
+      <c r="H40" t="s">
+        <v>432</v>
+      </c>
+      <c r="I40" t="s">
+        <v>433</v>
+      </c>
+      <c r="J40" t="s">
+        <v>434</v>
+      </c>
+      <c r="K40" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>436</v>
+      </c>
+      <c r="B41" t="s">
+        <v>437</v>
+      </c>
+      <c r="C41" t="s">
+        <v>438</v>
+      </c>
+      <c r="D41" t="s">
+        <v>439</v>
+      </c>
+      <c r="E41" t="s">
+        <v>440</v>
+      </c>
+      <c r="F41" t="s">
+        <v>441</v>
+      </c>
+      <c r="G41" t="s">
+        <v>442</v>
+      </c>
+      <c r="H41" t="s">
+        <v>443</v>
+      </c>
+      <c r="I41" t="s">
+        <v>444</v>
+      </c>
+      <c r="J41" t="s">
+        <v>445</v>
+      </c>
+      <c r="K41" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>447</v>
+      </c>
+      <c r="B42" t="s">
+        <v>448</v>
+      </c>
+      <c r="C42" t="s">
+        <v>449</v>
+      </c>
+      <c r="D42" t="s">
+        <v>450</v>
+      </c>
+      <c r="E42" t="s">
+        <v>408</v>
+      </c>
+      <c r="F42" t="s">
+        <v>451</v>
+      </c>
+      <c r="G42" t="s">
+        <v>452</v>
+      </c>
+      <c r="H42" t="s">
+        <v>453</v>
+      </c>
+      <c r="I42" t="s">
+        <v>454</v>
+      </c>
+      <c r="J42" t="s">
+        <v>455</v>
+      </c>
+      <c r="K42" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>457</v>
+      </c>
+      <c r="B43" t="s">
+        <v>458</v>
+      </c>
+      <c r="C43" t="s">
+        <v>459</v>
+      </c>
+      <c r="D43" t="s">
+        <v>460</v>
+      </c>
+      <c r="E43" t="s">
+        <v>461</v>
+      </c>
+      <c r="F43" t="s">
+        <v>462</v>
+      </c>
+      <c r="G43" t="s">
+        <v>463</v>
+      </c>
+      <c r="H43" t="s">
+        <v>464</v>
+      </c>
+      <c r="I43" t="s">
+        <v>465</v>
+      </c>
+      <c r="J43" t="s">
+        <v>466</v>
+      </c>
+      <c r="K43" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>468</v>
+      </c>
+      <c r="B44" t="s">
+        <v>469</v>
+      </c>
+      <c r="C44" t="s">
+        <v>470</v>
+      </c>
+      <c r="D44" t="s">
+        <v>471</v>
+      </c>
+      <c r="E44" t="s">
+        <v>472</v>
+      </c>
+      <c r="F44" t="s">
+        <v>473</v>
+      </c>
+      <c r="G44" t="s">
+        <v>474</v>
+      </c>
+      <c r="H44" t="s">
+        <v>475</v>
+      </c>
+      <c r="I44" t="s">
+        <v>476</v>
+      </c>
+      <c r="J44" t="s">
+        <v>477</v>
+      </c>
+      <c r="K44" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>479</v>
+      </c>
+      <c r="B45" t="s">
+        <v>480</v>
+      </c>
+      <c r="C45" t="s">
+        <v>481</v>
+      </c>
+      <c r="D45" t="s">
+        <v>482</v>
+      </c>
+      <c r="E45" t="s">
+        <v>331</v>
+      </c>
+      <c r="F45" t="s">
+        <v>483</v>
+      </c>
+      <c r="G45" t="s">
+        <v>484</v>
+      </c>
+      <c r="H45" t="s">
+        <v>485</v>
+      </c>
+      <c r="I45" t="s">
+        <v>486</v>
+      </c>
+      <c r="J45" t="s">
+        <v>487</v>
+      </c>
+      <c r="K45" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>489</v>
+      </c>
+      <c r="B46" t="s">
+        <v>490</v>
+      </c>
+      <c r="C46" t="s">
+        <v>491</v>
+      </c>
+      <c r="D46" t="s">
+        <v>407</v>
+      </c>
+      <c r="E46" t="s">
+        <v>408</v>
+      </c>
+      <c r="F46" t="s">
+        <v>492</v>
+      </c>
+      <c r="G46" t="s">
+        <v>410</v>
+      </c>
+      <c r="H46" t="s">
+        <v>493</v>
+      </c>
+      <c r="I46" t="s">
+        <v>494</v>
+      </c>
+      <c r="J46" t="s">
+        <v>495</v>
+      </c>
+      <c r="K46" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>497</v>
+      </c>
+      <c r="B47" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" t="s">
+        <v>499</v>
+      </c>
+      <c r="D47" t="s">
+        <v>500</v>
+      </c>
+      <c r="E47" t="s">
+        <v>501</v>
+      </c>
+      <c r="F47" t="s">
+        <v>502</v>
+      </c>
+      <c r="G47" t="s">
+        <v>503</v>
+      </c>
+      <c r="H47" t="s">
+        <v>504</v>
+      </c>
+      <c r="I47" t="s">
+        <v>505</v>
+      </c>
+      <c r="J47" t="s">
+        <v>506</v>
+      </c>
+      <c r="K47" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>508</v>
+      </c>
+      <c r="B48" t="s">
+        <v>509</v>
+      </c>
+      <c r="C48" t="s">
+        <v>510</v>
+      </c>
+      <c r="D48" t="s">
+        <v>511</v>
+      </c>
+      <c r="E48" t="s">
+        <v>512</v>
+      </c>
+      <c r="F48" t="s">
+        <v>513</v>
+      </c>
+      <c r="G48" t="s">
+        <v>514</v>
+      </c>
+      <c r="H48" t="s">
+        <v>515</v>
+      </c>
+      <c r="I48" t="s">
+        <v>516</v>
+      </c>
+      <c r="J48" t="s">
+        <v>517</v>
+      </c>
+      <c r="K48" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>519</v>
+      </c>
+      <c r="B49" t="s">
+        <v>520</v>
+      </c>
+      <c r="C49" t="s">
+        <v>521</v>
+      </c>
+      <c r="D49" t="s">
+        <v>522</v>
+      </c>
+      <c r="E49" t="s">
+        <v>523</v>
+      </c>
+      <c r="F49" t="s">
+        <v>524</v>
+      </c>
+      <c r="G49" t="s">
+        <v>525</v>
+      </c>
+      <c r="H49" t="s">
+        <v>526</v>
+      </c>
+      <c r="I49" t="s">
+        <v>527</v>
+      </c>
+      <c r="J49" t="s">
+        <v>528</v>
+      </c>
+      <c r="K49" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>530</v>
+      </c>
+      <c r="B50" t="s">
+        <v>531</v>
+      </c>
+      <c r="C50" t="s">
+        <v>532</v>
+      </c>
+      <c r="D50" t="s">
+        <v>533</v>
+      </c>
+      <c r="E50" t="s">
+        <v>440</v>
+      </c>
+      <c r="F50" t="s">
+        <v>534</v>
+      </c>
+      <c r="G50" t="s">
+        <v>535</v>
+      </c>
+      <c r="H50" t="s">
+        <v>536</v>
+      </c>
+      <c r="I50" t="s">
+        <v>537</v>
+      </c>
+      <c r="J50" t="s">
+        <v>538</v>
+      </c>
+      <c r="K50" t="s">
+        <v>539</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>